--- a/Results/Phase 2/Carbon dioxide/carbon dioxide human toxicity carcinogenic results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide human toxicity carcinogenic results.xlsx
@@ -2878,7 +2878,7 @@
         <v>2.325773062176766e-10</v>
       </c>
       <c r="J11" t="n">
-        <v>2.340521472922415e-10</v>
+        <v>2.340521472922414e-10</v>
       </c>
       <c r="K11" t="n">
         <v>2.325773062176766e-10</v>
@@ -3030,7 +3030,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.377903107215648e-10</v>
+        <v>2.377903107215649e-10</v>
       </c>
       <c r="C13" t="n">
         <v>2.670943431887203e-10</v>
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.679465060163961e-10</v>
+        <v>1.679465060163713e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>8.720089850731073e-11</v>
+        <v>8.720089850731099e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.810874684619881e-10</v>
+        <v>1.810874684619648e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>1.030484405412814e-10</v>
+        <v>1.030484405412808e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>1.065929076650378e-10</v>
+        <v>1.065929076650376e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>2.095646829869431e-10</v>
+        <v>2.095646829869163e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>8.762740020484498e-11</v>
+        <v>8.762740020482399e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>1.418657281551089e-10</v>
+        <v>1.418657281550871e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>1.790936406626084e-10</v>
+        <v>1.79093640662587e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.332710573227753e-10</v>
+        <v>1.332710573227527e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>2.462079324518604e-10</v>
+        <v>2.462079324518396e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>2.821190992966314e-10</v>
+        <v>2.821190992966308e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>9.187877270951783e-11</v>
+        <v>9.18787727094964e-11</v>
       </c>
       <c r="O2" t="n">
-        <v>1.121808340470528e-10</v>
+        <v>1.121808340470329e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>1.737552600687366e-10</v>
+        <v>1.737552600687167e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.183396674919206e-10</v>
+        <v>1.183396674918994e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>8.838716867318697e-11</v>
+        <v>8.838716867316551e-11</v>
       </c>
       <c r="S2" t="n">
-        <v>1.756433028194083e-10</v>
+        <v>1.756433028193887e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>9.841201673141193e-11</v>
+        <v>9.841201673139111e-11</v>
       </c>
       <c r="U2" t="n">
-        <v>2.342364903177555e-10</v>
+        <v>2.342364903177184e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>1.212737150842192e-10</v>
+        <v>1.21273715084218e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>2.016633784650683e-10</v>
+        <v>2.016633784650463e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>2.006437123319479e-10</v>
+        <v>2.006437123319256e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.277404877637545e-10</v>
+        <v>2.277404877637347e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.49272595937778e-10</v>
+        <v>1.492725959377565e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.092963224183805e-10</v>
+        <v>1.092963224183576e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.036380961948808e-10</v>
+        <v>4.03638096194882e-10</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.267367395922923e-10</v>
+        <v>1.267367395922691e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>1.874306162262639e-10</v>
+        <v>1.874306162262647e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>1.862497809154176e-10</v>
+        <v>1.862497809154116e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.497656789322916e-10</v>
+        <v>1.497656789322922e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.343931901017069e-10</v>
+        <v>1.343931901017071e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>1.985901977257274e-10</v>
+        <v>1.985901977257345e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.862497809154176e-10</v>
+        <v>1.862497809154116e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.862497809154176e-10</v>
+        <v>1.862497809154116e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.84058621654433e-10</v>
+        <v>1.840586216544198e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.862497809154176e-10</v>
+        <v>1.862497809154116e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.862497809154176e-10</v>
+        <v>1.862497809154116e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>1.840343786171354e-10</v>
+        <v>1.840343786171361e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>1.401172175771007e-10</v>
+        <v>1.4011721757708e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.527948465488931e-10</v>
+        <v>1.527948465488901e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.496872533529974e-10</v>
+        <v>1.496872533529985e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.150410686514198e-10</v>
+        <v>1.150410686513909e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.862497809154176e-10</v>
+        <v>1.862497809154116e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.862497809154176e-10</v>
+        <v>1.862497809154116e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>1.862497809154176e-10</v>
+        <v>1.862497809154116e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.572053676104738e-10</v>
+        <v>1.572053676104649e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>1.647685018612555e-10</v>
+        <v>1.64768501861253e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.862614769411069e-10</v>
+        <v>1.862614769410825e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>1.204955571476558e-10</v>
+        <v>1.204955571476347e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.454275599253394e-10</v>
+        <v>2.454275599253265e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.256312542950427e-10</v>
+        <v>1.256312542950373e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.862497809154176e-10</v>
+        <v>1.862497809154116e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.485784387915835e-10</v>
+        <v>2.485784387915842e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.312857624099658e-10</v>
+        <v>2.31285762409945e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>2.026053713418075e-10</v>
+        <v>2.026053713418039e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.360754889124138e-10</v>
+        <v>2.360754889123918e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>2.045837972204764e-10</v>
+        <v>2.045837972204745e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.078967538300591e-10</v>
+        <v>2.078967538300552e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>2.464550992104219e-10</v>
+        <v>2.464550992104e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>2.020103914962134e-10</v>
+        <v>2.020103914961929e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>2.217796251354826e-10</v>
+        <v>2.217796251354615e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>2.353273072041799e-10</v>
+        <v>2.353273072041706e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>2.186469685408176e-10</v>
+        <v>2.186469685407958e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>2.598111333536277e-10</v>
+        <v>2.598111333536049e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>2.714924178032085e-10</v>
+        <v>2.71492417803203e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>2.035599668520313e-10</v>
+        <v>2.035599668520102e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>2.109598298107216e-10</v>
+        <v>2.109598298107018e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>2.334029850522105e-10</v>
+        <v>2.334029850521877e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.132046522807026e-10</v>
+        <v>2.132046522806809e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.02287318181272e-10</v>
+        <v>2.022873181812516e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>2.340911544643121e-10</v>
+        <v>2.340911544642898e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>2.059412575807875e-10</v>
+        <v>2.059412575807648e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>2.554476832715171e-10</v>
+        <v>2.554476832714951e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>2.201047444468976e-10</v>
+        <v>2.201047444468956e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>2.435751664940013e-10</v>
+        <v>2.435751664939795e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>2.432035101620024e-10</v>
+        <v>2.432035101619845e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.530799666204951e-10</v>
+        <v>2.530799666204736e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.244793414664319e-10</v>
+        <v>2.2447934146641e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.099084591937157e-10</v>
+        <v>2.099084591936945e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.172957291881785e-10</v>
+        <v>3.172957291881713e-10</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.162652864578861e-10</v>
+        <v>2.162652864578673e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>2.391379264935984e-10</v>
+        <v>2.391379264935945e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.379570911827439e-10</v>
+        <v>2.379570911827395e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.216116820324897e-10</v>
+        <v>2.216116820324879e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.180296303308291e-10</v>
+        <v>2.180296303308229e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.424550282016128e-10</v>
+        <v>2.424550282016145e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>2.379570911827439e-10</v>
+        <v>2.379570911827395e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.379570911827439e-10</v>
+        <v>2.379570911827395e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>2.371369844739399e-10</v>
+        <v>2.371369844739364e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>2.379570911827439e-10</v>
+        <v>2.379570911827394e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>2.379570911827439e-10</v>
+        <v>2.379570911827395e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.357416888844724e-10</v>
+        <v>2.357416888844676e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>2.211423135618473e-10</v>
+        <v>2.211423135618265e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.257631604538421e-10</v>
+        <v>2.257631604538173e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>2.246304792251401e-10</v>
+        <v>2.246304792251141e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.120023517374299e-10</v>
+        <v>2.120023517374183e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>2.379570911827439e-10</v>
+        <v>2.379570911827395e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>2.379570911827439e-10</v>
+        <v>2.379570911827394e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.379570911827439e-10</v>
+        <v>2.379570911827394e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>2.273707435898197e-10</v>
+        <v>2.273707435898087e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.359580834855595e-10</v>
+        <v>2.359580834855786e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>2.379613542467701e-10</v>
+        <v>2.379613542467548e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>2.139904487444946e-10</v>
+        <v>2.139904487444632e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.59526696731281e-10</v>
+        <v>2.59526696731285e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.158623500483189e-10</v>
+        <v>2.15862350048291e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.379570911827439e-10</v>
+        <v>2.379570911827395e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.607783048670994e-10</v>
+        <v>2.607783048670987e-10</v>
       </c>
     </row>
     <row r="6">
@@ -5366,85 +5366,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.582963423481812e-11</v>
+        <v>8.582963423480138e-11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.714924316665779e-11</v>
+        <v>5.714924316665795e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>9.061936073726439e-11</v>
+        <v>9.061936073724935e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>5.912766904532955e-11</v>
+        <v>5.912766904532939e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>6.244062565491003e-11</v>
+        <v>6.244062565491021e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>9.740196156316997e-11</v>
+        <v>9.740196156314829e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>5.655426332106638e-11</v>
+        <v>5.655426332104982e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>7.632349696033493e-11</v>
+        <v>7.632349696031864e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>8.502429967564941e-11</v>
+        <v>8.502429967563992e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>7.319084036566996e-11</v>
+        <v>7.31908403656543e-11</v>
       </c>
       <c r="L6" t="n">
-        <v>1.143550051784781e-10</v>
+        <v>1.143550051784614e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.260362896280585e-10</v>
+        <v>1.260362896280576e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.810383867688349e-11</v>
+        <v>5.810383867686767e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>6.190669216346688e-11</v>
+        <v>6.190669216344828e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>8.434984740495523e-11</v>
+        <v>8.434984740493866e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.774852410555525e-11</v>
+        <v>6.77485241055381e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>5.683119000612536e-11</v>
+        <v>5.683119000610846e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>8.863502628916523e-11</v>
+        <v>8.863502628914866e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>6.048512940563946e-11</v>
+        <v>6.048512940562306e-11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.063945456242599e-10</v>
+        <v>1.063945456242443e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>6.206889664699619e-11</v>
+        <v>6.206889664699636e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>9.452202884674649e-11</v>
+        <v>9.452202884672917e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>9.415037251474818e-11</v>
+        <v>9.415037251472943e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.076238384453476e-10</v>
+        <v>1.076238384453306e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.902321329128497e-11</v>
+        <v>7.902321329126846e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.445233101856854e-11</v>
+        <v>6.445233101855191e-11</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.71839601013028e-10</v>
+        <v>1.718396010130284e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.080915828274158e-11</v>
+        <v>7.080915828272439e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>9.368179831844867e-11</v>
+        <v>9.368179831844884e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>9.250096300759496e-11</v>
+        <v>9.250096300759278e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>7.615555385734268e-11</v>
+        <v>7.615555385734266e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>7.257350215567811e-11</v>
+        <v>7.257350215567819e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>9.340189055435724e-11</v>
+        <v>9.340189055436237e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>9.250096300759496e-11</v>
+        <v>9.250096300759278e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>9.250096300759496e-11</v>
+        <v>9.250096300759278e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>8.68339769454283e-11</v>
+        <v>8.683397694541002e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>9.250096300759496e-11</v>
+        <v>9.250096300759278e-11</v>
       </c>
       <c r="L7" t="n">
-        <v>9.250096300759496e-11</v>
+        <v>9.250096300759278e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>9.028556070932276e-11</v>
+        <v>9.028556070932285e-11</v>
       </c>
       <c r="N7" t="n">
-        <v>7.568618538669842e-11</v>
+        <v>7.568618538667877e-11</v>
       </c>
       <c r="O7" t="n">
-        <v>7.671002280658556e-11</v>
+        <v>7.671002280656436e-11</v>
       </c>
       <c r="P7" t="n">
-        <v>7.557734157788342e-11</v>
+        <v>7.557734157786289e-11</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.654622356228224e-11</v>
+        <v>6.654622356227681e-11</v>
       </c>
       <c r="R7" t="n">
-        <v>9.250096300759496e-11</v>
+        <v>9.250096300759278e-11</v>
       </c>
       <c r="S7" t="n">
-        <v>9.250096300759496e-11</v>
+        <v>9.250096300759278e-11</v>
       </c>
       <c r="T7" t="n">
-        <v>9.250096300759496e-11</v>
+        <v>9.250096300759278e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>7.831760594256419e-11</v>
+        <v>7.831760594255579e-11</v>
       </c>
       <c r="V7" t="n">
-        <v>7.792223568565331e-11</v>
+        <v>7.792223568565291e-11</v>
       </c>
       <c r="W7" t="n">
-        <v>8.890821659951353e-11</v>
+        <v>8.890821659950432e-11</v>
       </c>
       <c r="X7" t="n">
-        <v>6.493731109723917e-11</v>
+        <v>6.493731109721314e-11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.140705685561333e-10</v>
+        <v>1.14070568556145e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.040622187317015e-11</v>
+        <v>7.040622187314345e-11</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.250096300759496e-11</v>
+        <v>9.250096300759278e-11</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.153221766919523e-10</v>
+        <v>1.153221766919522e-10</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="C8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="E8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="F8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="G8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="H8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="I8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="J8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="K8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="L8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="M8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="N8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="O8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="P8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="R8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="S8" t="n">
-        <v>1.721641328299292e-10</v>
+        <v>1.721641328299296e-10</v>
       </c>
       <c r="T8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="U8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="V8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="W8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="X8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.711036367362486e-10</v>
+        <v>1.711036367362488e-10</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1803828900583e-10</v>
+        <v>2.180382890058308e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.299916959597938e-10</v>
+        <v>1.29991695959794e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>2.32160920635565e-10</v>
+        <v>2.321609206355695e-10</v>
       </c>
       <c r="E9" t="n">
-        <v>1.534455200194606e-10</v>
+        <v>1.534455200194601e-10</v>
       </c>
       <c r="F9" t="n">
-        <v>1.538370234726466e-10</v>
+        <v>1.538370234726468e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>2.62765468228024e-10</v>
+        <v>2.627654682280251e-10</v>
       </c>
       <c r="H9" t="n">
-        <v>1.317191058483769e-10</v>
+        <v>1.317191058483772e-10</v>
       </c>
       <c r="I9" t="n">
-        <v>1.900091990607889e-10</v>
+        <v>1.90009199060789e-10</v>
       </c>
       <c r="J9" t="n">
-        <v>2.323729933473483e-10</v>
+        <v>2.323729933473507e-10</v>
       </c>
       <c r="K9" t="n">
-        <v>1.807724806205348e-10</v>
+        <v>1.807724806205344e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>3.021460779856584e-10</v>
+        <v>3.021460779856551e-10</v>
       </c>
       <c r="M9" t="n">
-        <v>3.431208158362875e-10</v>
+        <v>3.431208158362863e-10</v>
       </c>
       <c r="N9" t="n">
-        <v>1.362880685900992e-10</v>
+        <v>1.362880685900993e-10</v>
       </c>
       <c r="O9" t="n">
         <v>1.581067546095904e-10</v>
       </c>
       <c r="P9" t="n">
-        <v>2.242809743531621e-10</v>
+        <v>2.242809743531637e-10</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.64725671326755e-10</v>
+        <v>1.64725671326754e-10</v>
       </c>
       <c r="R9" t="n">
-        <v>1.325356312928947e-10</v>
+        <v>1.325356312928946e-10</v>
       </c>
       <c r="S9" t="n">
-        <v>2.26310059542267e-10</v>
+        <v>2.263100595422667e-10</v>
       </c>
       <c r="T9" t="n">
-        <v>1.433093654738239e-10</v>
+        <v>1.433093654738247e-10</v>
       </c>
       <c r="U9" t="n">
-        <v>2.892803333313638e-10</v>
+        <v>2.892803333313671e-10</v>
       </c>
       <c r="V9" t="n">
-        <v>1.734876635184732e-10</v>
+        <v>1.73487663518476e-10</v>
       </c>
       <c r="W9" t="n">
-        <v>2.542739126346836e-10</v>
+        <v>2.54273912634683e-10</v>
       </c>
       <c r="X9" t="n">
-        <v>2.531780743927738e-10</v>
+        <v>2.531780743927725e-10</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.822990599645304e-10</v>
+        <v>2.822990599645272e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.979693820122187e-10</v>
+        <v>1.979693820122172e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.550067613380092e-10</v>
+        <v>1.550067613380085e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.711623108169905e-10</v>
+        <v>4.711623108169915e-10</v>
       </c>
     </row>
     <row r="10">
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.73750029818979e-10</v>
+        <v>1.737500298189791e-10</v>
       </c>
       <c r="C10" t="n">
-        <v>2.377088732638006e-10</v>
+        <v>2.377088732638012e-10</v>
       </c>
       <c r="D10" t="n">
-        <v>2.377088732638006e-10</v>
+        <v>2.377088732638012e-10</v>
       </c>
       <c r="E10" t="n">
-        <v>2.036526757956407e-10</v>
+        <v>2.03652675795641e-10</v>
       </c>
       <c r="F10" t="n">
-        <v>1.837140701259056e-10</v>
+        <v>1.837140701259061e-10</v>
       </c>
       <c r="G10" t="n">
-        <v>2.509711561058077e-10</v>
+        <v>2.50971156105808e-10</v>
       </c>
       <c r="H10" t="n">
-        <v>2.377088732638006e-10</v>
+        <v>2.377088732638012e-10</v>
       </c>
       <c r="I10" t="n">
-        <v>2.377088732638006e-10</v>
+        <v>2.377088732638012e-10</v>
       </c>
       <c r="J10" t="n">
-        <v>2.377088732638006e-10</v>
+        <v>2.377088732638012e-10</v>
       </c>
       <c r="K10" t="n">
-        <v>2.377088732638006e-10</v>
+        <v>2.377088732638012e-10</v>
       </c>
       <c r="L10" t="n">
-        <v>2.377088732638006e-10</v>
+        <v>2.377088732638012e-10</v>
       </c>
       <c r="M10" t="n">
-        <v>2.377088732637966e-10</v>
+        <v>2.377088732637972e-10</v>
       </c>
       <c r="N10" t="n">
-        <v>1.881300695148291e-10</v>
+        <v>1.881300695148295e-10</v>
       </c>
       <c r="O10" t="n">
-        <v>2.017547552749933e-10</v>
+        <v>2.017547552749931e-10</v>
       </c>
       <c r="P10" t="n">
-        <v>1.984150155761418e-10</v>
+        <v>1.984150155761425e-10</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.611806572905587e-10</v>
+        <v>1.611806572905591e-10</v>
       </c>
       <c r="R10" t="n">
-        <v>2.377088732638006e-10</v>
+        <v>2.377088732638012e-10</v>
       </c>
       <c r="S10" t="n">
-        <v>2.377088732638006e-10</v>
+        <v>2.377088732638012e-10</v>
       </c>
       <c r="T10" t="n">
-        <v>2.377088732638006e-10</v>
+        <v>2.377088732638012e-10</v>
       </c>
       <c r="U10" t="n">
-        <v>2.064947554466476e-10</v>
+        <v>2.064947554466481e-10</v>
       </c>
       <c r="V10" t="n">
-        <v>2.202316409104806e-10</v>
+        <v>2.202316409104809e-10</v>
       </c>
       <c r="W10" t="n">
-        <v>2.377214430175616e-10</v>
+        <v>2.37721443017562e-10</v>
       </c>
       <c r="X10" t="n">
-        <v>1.670426123855538e-10</v>
+        <v>1.67042612385554e-10</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.013074092982185e-10</v>
+        <v>3.013074092982189e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.725619614648117e-10</v>
+        <v>1.725619614648121e-10</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.377088732638006e-10</v>
+        <v>2.377088732638012e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.045192334011287e-10</v>
+        <v>3.045192334011294e-10</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="C11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="D11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="E11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="G11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="H11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="I11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="J11" t="n">
-        <v>2.506113314702878e-10</v>
+        <v>2.506113314702809e-10</v>
       </c>
       <c r="K11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="L11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="M11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="N11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="O11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="P11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="R11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="S11" t="n">
-        <v>2.499536649588723e-10</v>
+        <v>2.499536649588695e-10</v>
       </c>
       <c r="T11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="U11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="V11" t="n">
-        <v>2.572979473584537e-10</v>
+        <v>2.572979473584292e-10</v>
       </c>
       <c r="W11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="X11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.494324041565315e-10</v>
+        <v>2.494324041565251e-10</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.725019794670209e-10</v>
+        <v>2.725019794670196e-10</v>
       </c>
       <c r="C12" t="n">
-        <v>2.292248396377771e-10</v>
+        <v>2.292248396377736e-10</v>
       </c>
       <c r="D12" t="n">
-        <v>2.79443612103248e-10</v>
+        <v>2.794436121032445e-10</v>
       </c>
       <c r="E12" t="n">
-        <v>2.407529906796915e-10</v>
+        <v>2.407529906796872e-10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.409454245842968e-10</v>
+        <v>2.409454245842959e-10</v>
       </c>
       <c r="G12" t="n">
-        <v>2.944865256306006e-10</v>
+        <v>2.944865256305986e-10</v>
       </c>
       <c r="H12" t="n">
-        <v>2.300739055323714e-10</v>
+        <v>2.300739055323664e-10</v>
       </c>
       <c r="I12" t="n">
-        <v>2.587249688766882e-10</v>
+        <v>2.587249688766845e-10</v>
       </c>
       <c r="J12" t="n">
-        <v>2.807267785486287e-10</v>
+        <v>2.807267785486259e-10</v>
       </c>
       <c r="K12" t="n">
-        <v>2.541848868397465e-10</v>
+        <v>2.541848868397438e-10</v>
       </c>
       <c r="L12" t="n">
-        <v>3.138430969195208e-10</v>
+        <v>3.138430969195168e-10</v>
       </c>
       <c r="M12" t="n">
-        <v>3.339832227106597e-10</v>
+        <v>3.339832227106529e-10</v>
       </c>
       <c r="N12" t="n">
-        <v>2.323196669253726e-10</v>
+        <v>2.323196669253701e-10</v>
       </c>
       <c r="O12" t="n">
-        <v>2.430441060329966e-10</v>
+        <v>2.43044106032994e-10</v>
       </c>
       <c r="P12" t="n">
-        <v>2.755704180895732e-10</v>
+        <v>2.755704180895688e-10</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.462974719427587e-10</v>
+        <v>2.462974719427575e-10</v>
       </c>
       <c r="R12" t="n">
-        <v>2.304752485555831e-10</v>
+        <v>2.304752485555792e-10</v>
       </c>
       <c r="S12" t="n">
-        <v>2.765677650670805e-10</v>
+        <v>2.765677650670776e-10</v>
       </c>
       <c r="T12" t="n">
-        <v>2.357708129210025e-10</v>
+        <v>2.357708129209982e-10</v>
       </c>
       <c r="U12" t="n">
-        <v>3.075192561989588e-10</v>
+        <v>3.075192561989671e-10</v>
       </c>
       <c r="V12" t="n">
-        <v>2.584697571564412e-10</v>
+        <v>2.584697571564498e-10</v>
       </c>
       <c r="W12" t="n">
-        <v>2.903127100851367e-10</v>
+        <v>2.903127100851335e-10</v>
       </c>
       <c r="X12" t="n">
-        <v>2.897740777180608e-10</v>
+        <v>2.897740777180575e-10</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.040877827798271e-10</v>
+        <v>3.040877827798247e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.626376012539035e-10</v>
+        <v>2.626376012539004e-10</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.415203804958395e-10</v>
+        <v>2.415203804958364e-10</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.969188740575319e-10</v>
+        <v>3.969188740575281e-10</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.507331736641552e-10</v>
+        <v>2.507331736641501e-10</v>
       </c>
       <c r="C13" t="n">
-        <v>2.821705719247672e-10</v>
+        <v>2.821705719247617e-10</v>
       </c>
       <c r="D13" t="n">
-        <v>2.821705719247672e-10</v>
+        <v>2.821705719247617e-10</v>
       </c>
       <c r="E13" t="n">
-        <v>2.654310846954174e-10</v>
+        <v>2.654310846954131e-10</v>
       </c>
       <c r="F13" t="n">
-        <v>2.556307528970231e-10</v>
+        <v>2.556307528970214e-10</v>
       </c>
       <c r="G13" t="n">
-        <v>2.886893212500068e-10</v>
+        <v>2.88689321250004e-10</v>
       </c>
       <c r="H13" t="n">
-        <v>2.821705719247672e-10</v>
+        <v>2.821705719247617e-10</v>
       </c>
       <c r="I13" t="n">
-        <v>2.821705719247672e-10</v>
+        <v>2.821705719247617e-10</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8334949923852e-10</v>
+        <v>2.833494992385192e-10</v>
       </c>
       <c r="K13" t="n">
-        <v>2.821705719247672e-10</v>
+        <v>2.821705719247617e-10</v>
       </c>
       <c r="L13" t="n">
-        <v>2.821705719247672e-10</v>
+        <v>2.821705719247617e-10</v>
       </c>
       <c r="M13" t="n">
-        <v>2.821705719247655e-10</v>
+        <v>2.821705719247597e-10</v>
       </c>
       <c r="N13" t="n">
-        <v>2.578013289117054e-10</v>
+        <v>2.578013289117024e-10</v>
       </c>
       <c r="O13" t="n">
-        <v>2.644982084884527e-10</v>
+        <v>2.644982084884503e-10</v>
       </c>
       <c r="P13" t="n">
-        <v>2.628566414846636e-10</v>
+        <v>2.628566414846596e-10</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.445550073812872e-10</v>
+        <v>2.445550073812862e-10</v>
       </c>
       <c r="R13" t="n">
-        <v>2.821705719247672e-10</v>
+        <v>2.821705719247617e-10</v>
       </c>
       <c r="S13" t="n">
-        <v>2.821705719247672e-10</v>
+        <v>2.821705719247617e-10</v>
       </c>
       <c r="T13" t="n">
-        <v>2.821705719247672e-10</v>
+        <v>2.821705719247617e-10</v>
       </c>
       <c r="U13" t="n">
-        <v>2.668280391283729e-10</v>
+        <v>2.668280391283723e-10</v>
       </c>
       <c r="V13" t="n">
-        <v>2.814456109150418e-10</v>
+        <v>2.81445610915007e-10</v>
       </c>
       <c r="W13" t="n">
-        <v>2.821767502784358e-10</v>
+        <v>2.821767502784322e-10</v>
       </c>
       <c r="X13" t="n">
-        <v>2.474363074014529e-10</v>
+        <v>2.474363074014479e-10</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.134308699292294e-10</v>
+        <v>3.134308699292279e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.501492078511526e-10</v>
+        <v>2.501492078511511e-10</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.821705719247672e-10</v>
+        <v>2.821705719247617e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.150095631642524e-10</v>
+        <v>3.150095631642508e-10</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="C14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="D14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="E14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="F14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="G14" t="n">
-        <v>1.212656954591501e-10</v>
+        <v>1.212656954591505e-10</v>
       </c>
       <c r="H14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="I14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="J14" t="n">
-        <v>1.213698971172491e-10</v>
+        <v>1.213698971172492e-10</v>
       </c>
       <c r="K14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="L14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="M14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="N14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="O14" t="n">
-        <v>1.212656954591501e-10</v>
+        <v>1.212656954591505e-10</v>
       </c>
       <c r="P14" t="n">
-        <v>1.212656954591501e-10</v>
+        <v>1.212656954591505e-10</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="R14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="S14" t="n">
-        <v>1.248799261410273e-10</v>
+        <v>1.248799261410277e-10</v>
       </c>
       <c r="T14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="U14" t="n">
-        <v>1.212656954591501e-10</v>
+        <v>1.212656954591505e-10</v>
       </c>
       <c r="V14" t="n">
-        <v>1.214072523462177e-10</v>
+        <v>1.21407252346218e-10</v>
       </c>
       <c r="W14" t="n">
-        <v>1.212656954591501e-10</v>
+        <v>1.212656954591505e-10</v>
       </c>
       <c r="X14" t="n">
-        <v>1.212656954591501e-10</v>
+        <v>1.212656954591505e-10</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.243586653386863e-10</v>
+        <v>1.243586653386865e-10</v>
       </c>
     </row>
     <row r="15">
@@ -6158,85 +6158,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.474282406491767e-10</v>
+        <v>1.474282406491766e-10</v>
       </c>
       <c r="C15" t="n">
-        <v>1.041511008199324e-10</v>
+        <v>1.041511008199326e-10</v>
       </c>
       <c r="D15" t="n">
-        <v>1.543698732854034e-10</v>
+        <v>1.543698732854032e-10</v>
       </c>
       <c r="E15" t="n">
-        <v>1.156792518618467e-10</v>
+        <v>1.156792518618468e-10</v>
       </c>
       <c r="F15" t="n">
-        <v>1.158716857664537e-10</v>
+        <v>1.158716857664539e-10</v>
       </c>
       <c r="G15" t="n">
-        <v>1.663198169332238e-10</v>
+        <v>1.663198169332202e-10</v>
       </c>
       <c r="H15" t="n">
-        <v>1.050001667145267e-10</v>
+        <v>1.05000166714527e-10</v>
       </c>
       <c r="I15" t="n">
-        <v>1.33651230058843e-10</v>
+        <v>1.336512300588428e-10</v>
       </c>
       <c r="J15" t="n">
-        <v>1.514853441955958e-10</v>
+        <v>1.514853441955942e-10</v>
       </c>
       <c r="K15" t="n">
-        <v>1.291111480219017e-10</v>
+        <v>1.291111480219013e-10</v>
       </c>
       <c r="L15" t="n">
         <v>1.887693581016763e-10</v>
       </c>
       <c r="M15" t="n">
-        <v>2.089094838928143e-10</v>
+        <v>2.089094838928145e-10</v>
       </c>
       <c r="N15" t="n">
-        <v>1.072459281075286e-10</v>
+        <v>1.072459281075287e-10</v>
       </c>
       <c r="O15" t="n">
-        <v>1.148773973356154e-10</v>
+        <v>1.148773973356168e-10</v>
       </c>
       <c r="P15" t="n">
-        <v>1.474037093921913e-10</v>
+        <v>1.474037093921914e-10</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.212237331249158e-10</v>
+        <v>1.21223733124916e-10</v>
       </c>
       <c r="R15" t="n">
-        <v>1.05401509737738e-10</v>
+        <v>1.054015097377379e-10</v>
       </c>
       <c r="S15" t="n">
-        <v>1.514940262492353e-10</v>
+        <v>1.514940262492355e-10</v>
       </c>
       <c r="T15" t="n">
-        <v>1.106970741031574e-10</v>
+        <v>1.106970741031575e-10</v>
       </c>
       <c r="U15" t="n">
-        <v>1.793525475015784e-10</v>
+        <v>1.793525475015725e-10</v>
       </c>
       <c r="V15" t="n">
-        <v>1.225790621442079e-10</v>
+        <v>1.225790621442069e-10</v>
       </c>
       <c r="W15" t="n">
-        <v>1.621460013877556e-10</v>
+        <v>1.621460013877557e-10</v>
       </c>
       <c r="X15" t="n">
-        <v>1.616073690206799e-10</v>
+        <v>1.616073690206802e-10</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.79014043961982e-10</v>
+        <v>1.790140439619831e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.375638624360582e-10</v>
+        <v>1.375638624360571e-10</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.164466416779946e-10</v>
+        <v>1.164466416779945e-10</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.71845135239688e-10</v>
+        <v>2.718451352396863e-10</v>
       </c>
     </row>
     <row r="16">
@@ -6246,85 +6246,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.256594348463104e-10</v>
+        <v>1.256594348463107e-10</v>
       </c>
       <c r="C16" t="n">
-        <v>1.570968331069225e-10</v>
+        <v>1.570968331069227e-10</v>
       </c>
       <c r="D16" t="n">
-        <v>1.570968331069225e-10</v>
+        <v>1.570968331069227e-10</v>
       </c>
       <c r="E16" t="n">
-        <v>1.403573458775724e-10</v>
+        <v>1.403573458775726e-10</v>
       </c>
       <c r="F16" t="n">
-        <v>1.305570140791788e-10</v>
+        <v>1.30557014079179e-10</v>
       </c>
       <c r="G16" t="n">
-        <v>1.605226125526265e-10</v>
+        <v>1.605226125526267e-10</v>
       </c>
       <c r="H16" t="n">
-        <v>1.570968331069225e-10</v>
+        <v>1.570968331069227e-10</v>
       </c>
       <c r="I16" t="n">
-        <v>1.570968331069225e-10</v>
+        <v>1.570968331069227e-10</v>
       </c>
       <c r="J16" t="n">
-        <v>1.541080648854855e-10</v>
+        <v>1.541080648854859e-10</v>
       </c>
       <c r="K16" t="n">
-        <v>1.570968331069225e-10</v>
+        <v>1.570968331069227e-10</v>
       </c>
       <c r="L16" t="n">
-        <v>1.570968331069225e-10</v>
+        <v>1.570968331069227e-10</v>
       </c>
       <c r="M16" t="n">
-        <v>1.570968331069206e-10</v>
+        <v>1.570968331069209e-10</v>
       </c>
       <c r="N16" t="n">
-        <v>1.327275900938619e-10</v>
+        <v>1.327275900938622e-10</v>
       </c>
       <c r="O16" t="n">
-        <v>1.363314997910724e-10</v>
+        <v>1.363314997910728e-10</v>
       </c>
       <c r="P16" t="n">
-        <v>1.346899327872831e-10</v>
+        <v>1.346899327872834e-10</v>
       </c>
       <c r="Q16" t="n">
         <v>1.194812685634438e-10</v>
       </c>
       <c r="R16" t="n">
-        <v>1.570968331069225e-10</v>
+        <v>1.570968331069227e-10</v>
       </c>
       <c r="S16" t="n">
-        <v>1.570968331069225e-10</v>
+        <v>1.570968331069227e-10</v>
       </c>
       <c r="T16" t="n">
-        <v>1.570968331069225e-10</v>
+        <v>1.570968331069227e-10</v>
       </c>
       <c r="U16" t="n">
-        <v>1.386613304309941e-10</v>
+        <v>1.386613304309943e-10</v>
       </c>
       <c r="V16" t="n">
-        <v>1.455549159028105e-10</v>
+        <v>1.455549159028108e-10</v>
       </c>
       <c r="W16" t="n">
         <v>1.540100415810551e-10</v>
       </c>
       <c r="X16" t="n">
-        <v>1.192695987040706e-10</v>
+        <v>1.192695987040709e-10</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.883571311113851e-10</v>
+        <v>1.883571311113856e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.250754690333104e-10</v>
+        <v>1.250754690333107e-10</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.570968331069225e-10</v>
+        <v>1.570968331069227e-10</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.89935824346408e-10</v>
+        <v>1.899358243464084e-10</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.547037637550828e-10</v>
+        <v>1.547037637550784e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>8.162363145617512e-11</v>
+        <v>8.162363145617466e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.595374187040521e-10</v>
+        <v>1.595374187040383e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>9.134454942527459e-11</v>
+        <v>9.134454942527611e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.150688376160734e-10</v>
+        <v>1.150688376160718e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>1.960355311264041e-10</v>
+        <v>1.960355311263857e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>9.09364729527099e-11</v>
+        <v>9.093647295270308e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>1.32235597962711e-10</v>
+        <v>1.322355979627005e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>1.724822680637202e-10</v>
+        <v>1.724822680637084e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.303768626960498e-10</v>
+        <v>1.303768626960479e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>2.210523968156824e-10</v>
+        <v>2.210523968156708e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>2.550954443340605e-10</v>
+        <v>2.550954443340608e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>7.848339094652936e-11</v>
+        <v>7.848339094652119e-11</v>
       </c>
       <c r="O2" t="n">
-        <v>1.051727396818247e-10</v>
+        <v>1.05172739681814e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6403348356531e-10</v>
+        <v>1.640334835652985e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.142536986209513e-10</v>
+        <v>1.14253698620942e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>1.063476931309118e-10</v>
+        <v>1.063476931309019e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>1.719344797239023e-10</v>
+        <v>1.719344797238916e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>1.084695563142522e-10</v>
+        <v>1.08469556314243e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>2.421647485421302e-10</v>
+        <v>2.421647485421171e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>1.49596842552759e-10</v>
+        <v>1.495968425527519e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>2.016712548389277e-10</v>
+        <v>2.016712548389244e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>2.176140488274637e-10</v>
+        <v>2.17614048827454e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.115883473485731e-10</v>
+        <v>3.115883473485619e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.476845255673543e-10</v>
+        <v>1.476845255673437e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.132819080383428e-10</v>
+        <v>1.132819080383324e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.813237680538865e-10</v>
+        <v>3.813237680538798e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.253209211411387e-10</v>
+        <v>1.253209211411204e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>1.85160329206375e-10</v>
+        <v>1.851603292063748e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>1.83993077651637e-10</v>
+        <v>1.839930776516315e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.48011592830115e-10</v>
+        <v>1.480115928301157e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.329063258327168e-10</v>
+        <v>1.329063258327153e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>1.961591315181753e-10</v>
+        <v>1.961591315181756e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83993077651637e-10</v>
+        <v>1.839930776516315e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.83993077651637e-10</v>
+        <v>1.839930776516315e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.818543289975613e-10</v>
+        <v>1.818543289975603e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.83993077651637e-10</v>
+        <v>1.839930776516315e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.83993077651637e-10</v>
+        <v>1.839930776516315e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>1.817458090002731e-10</v>
+        <v>1.817458090002718e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>1.385123407199706e-10</v>
+        <v>1.385123407199575e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.510108421353066e-10</v>
+        <v>1.510108421352986e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.479471574318571e-10</v>
+        <v>1.479471574318527e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.137905032583148e-10</v>
+        <v>1.137905032583131e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.83993077651637e-10</v>
+        <v>1.839930776516315e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.83993077651637e-10</v>
+        <v>1.839930776516315e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83993077651637e-10</v>
+        <v>1.839930776516315e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.553675456302264e-10</v>
+        <v>1.553675456302216e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>1.62886228398558e-10</v>
+        <v>1.628862283985537e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.840046084189533e-10</v>
+        <v>1.840046084189472e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>1.191679229903704e-10</v>
+        <v>1.191679229903641e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.423492508653177e-10</v>
+        <v>2.423492508653168e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.242310557110499e-10</v>
+        <v>1.242310557110521e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.83993077651637e-10</v>
+        <v>1.839930776516315e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.453785124208374e-10</v>
+        <v>2.453785124208377e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.251781196643533e-10</v>
+        <v>2.251781196643494e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.992830716612368e-10</v>
+        <v>1.992830716612391e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.269399301336101e-10</v>
+        <v>2.269399301335979e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.990719186870797e-10</v>
+        <v>1.99071918687084e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.097434136757654e-10</v>
+        <v>2.097434136757651e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>2.402430635290828e-10</v>
+        <v>2.402430635290677e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>2.019356909602221e-10</v>
+        <v>2.019356909602189e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>2.169887370675573e-10</v>
+        <v>2.169887370675477e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>2.320274422567414e-10</v>
+        <v>2.320274422567398e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>2.163112498892296e-10</v>
+        <v>2.163112498892274e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>2.493614173099574e-10</v>
+        <v>2.493614173099462e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>2.603415427600584e-10</v>
+        <v>2.603415427600613e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.97396688800442e-10</v>
+        <v>1.973966888004252e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>2.071246430123011e-10</v>
+        <v>2.071246430122848e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>2.285786929800797e-10</v>
+        <v>2.285786929800679e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.104345459116084e-10</v>
+        <v>2.104345459115943e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.075528997474927e-10</v>
+        <v>2.075528997474817e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>2.314585133017066e-10</v>
+        <v>2.314585133016883e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>2.083262939616443e-10</v>
+        <v>2.083262939616285e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>2.570566216004973e-10</v>
+        <v>2.570566216004844e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>2.316179175448874e-10</v>
+        <v>2.31617917544881e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>2.422972186442895e-10</v>
+        <v>2.422972186442977e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>2.481081798433722e-10</v>
+        <v>2.481081798433617e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.823607081523903e-10</v>
+        <v>2.823607081523739e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.226196897689826e-10</v>
+        <v>2.226196897689625e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.100803396555886e-10</v>
+        <v>2.100803396555898e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.078403878626697e-10</v>
+        <v>3.07840387862664e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.144684185623287e-10</v>
+        <v>2.144684185623278e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>2.370209822018975e-10</v>
+        <v>2.370209822018974e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.358537306471593e-10</v>
+        <v>2.358537306471585e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.197263905901247e-10</v>
+        <v>2.1972639059013e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.162449686723701e-10</v>
+        <v>2.162449686723727e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.402881144204949e-10</v>
+        <v>2.402881144204888e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>2.358537306471593e-10</v>
+        <v>2.358537306471585e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.358537306471593e-10</v>
+        <v>2.358537306471585e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3544344841483e-10</v>
+        <v>2.35443448414827e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>2.358537306471593e-10</v>
+        <v>2.358537306471585e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>2.358537306471593e-10</v>
+        <v>2.358537306471585e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.336064619957966e-10</v>
+        <v>2.336064619957969e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>2.192765360973432e-10</v>
+        <v>2.192765360973274e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.238320930984202e-10</v>
+        <v>2.238320930984096e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22715415999615e-10</v>
+        <v>2.227154159996027e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.102657166410419e-10</v>
+        <v>2.10265716641037e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>2.358537306471593e-10</v>
+        <v>2.358537306471585e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>2.358537306471593e-10</v>
+        <v>2.358537306471585e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.358537306471593e-10</v>
+        <v>2.358537306471585e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>2.254200603633222e-10</v>
+        <v>2.254200603633168e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.364617426338283e-10</v>
+        <v>2.364617426338236e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>2.358579334764449e-10</v>
+        <v>2.358579334764442e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>2.122257229885256e-10</v>
+        <v>2.122257229885105e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.571238705307618e-10</v>
+        <v>2.57123870530759e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.140711754109073e-10</v>
+        <v>2.140711754108872e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.358537306471593e-10</v>
+        <v>2.358537306471585e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.582899385342115e-10</v>
+        <v>2.582899385342084e-10</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.093280433676615e-11</v>
+        <v>8.093280433675706e-11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.50377563336495e-11</v>
+        <v>5.503775633365002e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>8.269461480602282e-11</v>
+        <v>8.269461480600881e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>5.482660335949243e-11</v>
+        <v>5.482660335949139e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>6.549809834817797e-11</v>
+        <v>6.5498098348179e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>9.241202332611201e-11</v>
+        <v>9.241202332609792e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>5.769037563263472e-11</v>
+        <v>5.769037563262614e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>7.274342173996977e-11</v>
+        <v>7.274342173995574e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>8.258873480906283e-11</v>
+        <v>8.258873480906085e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>7.206593456164243e-11</v>
+        <v>7.20659345616379e-11</v>
       </c>
       <c r="L6" t="n">
-        <v>1.051161019823698e-10</v>
+        <v>1.05116101982354e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.16096227432471e-10</v>
+        <v>1.160962274324722e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.315137347285479e-11</v>
+        <v>5.315137347284229e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>5.929360280932986e-11</v>
+        <v>5.929360280931684e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>8.074765277710891e-11</v>
+        <v>8.074765277709415e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.618923058402114e-11</v>
+        <v>6.618923058400682e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>6.330758441990535e-11</v>
+        <v>6.330758441989186e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>8.721319797411907e-11</v>
+        <v>8.721319797410501e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>6.408097863405742e-11</v>
+        <v>6.408097863404391e-11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.092255813975261e-10</v>
+        <v>1.092255813975113e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>7.241906740340562e-11</v>
+        <v>7.241906740340071e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>9.446617844131853e-11</v>
+        <v>9.446617844132636e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.002771396404011e-10</v>
+        <v>1.002771396403877e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.381153928248028e-10</v>
+        <v>1.381153928247911e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.837437444139527e-11</v>
+        <v>7.837437444138235e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.583502432800145e-11</v>
+        <v>6.583502432799477e-11</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.635950725350824e-10</v>
+        <v>1.635950725350839e-10</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.022310323474133e-11</v>
+        <v>7.022310323473665e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>9.277566687430973e-11</v>
+        <v>9.277566687431167e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>9.16084153195719e-11</v>
+        <v>9.16084153195733e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>7.548107526253755e-11</v>
+        <v>7.548107526253577e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>7.199965334478267e-11</v>
+        <v>7.199965334478386e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>9.245707421752409e-11</v>
+        <v>9.245707421751766e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>9.16084153195719e-11</v>
+        <v>9.16084153195733e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>9.16084153195719e-11</v>
+        <v>9.16084153195733e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>8.600474096715301e-11</v>
+        <v>8.60047409671492e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>9.16084153195719e-11</v>
+        <v>9.16084153195733e-11</v>
       </c>
       <c r="L7" t="n">
-        <v>9.16084153195719e-11</v>
+        <v>9.16084153195733e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>8.936114666820961e-11</v>
+        <v>8.936114666820931e-11</v>
       </c>
       <c r="N7" t="n">
-        <v>7.503122076975588e-11</v>
+        <v>7.503122076974005e-11</v>
       </c>
       <c r="O7" t="n">
-        <v>7.600105289544908e-11</v>
+        <v>7.600105289543703e-11</v>
       </c>
       <c r="P7" t="n">
-        <v>7.488437579664387e-11</v>
+        <v>7.48843757966349e-11</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.602040131345463e-11</v>
+        <v>6.602040131344522e-11</v>
       </c>
       <c r="R7" t="n">
-        <v>9.16084153195719e-11</v>
+        <v>9.16084153195733e-11</v>
       </c>
       <c r="S7" t="n">
-        <v>9.16084153195719e-11</v>
+        <v>9.16084153195733e-11</v>
       </c>
       <c r="T7" t="n">
-        <v>9.16084153195719e-11</v>
+        <v>9.16084153195733e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>7.758902016035125e-11</v>
+        <v>7.758902016034526e-11</v>
       </c>
       <c r="V7" t="n">
-        <v>7.726289249235199e-11</v>
+        <v>7.726289249235312e-11</v>
       </c>
       <c r="W7" t="n">
-        <v>8.8026893273474e-11</v>
+        <v>8.802689327347247e-11</v>
       </c>
       <c r="X7" t="n">
-        <v>6.439468278555463e-11</v>
+        <v>6.439468278553813e-11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.128785552031749e-10</v>
+        <v>1.128785552031686e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.982586008331988e-11</v>
+        <v>6.982586008330141e-11</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.16084153195719e-11</v>
+        <v>9.16084153195733e-11</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.140446232066241e-10</v>
+        <v>1.140446232066227e-10</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="C8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="E8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="F8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="G8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="H8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="I8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="J8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="K8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="L8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932566e-10</v>
       </c>
       <c r="M8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="N8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="O8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="P8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="S8" t="n">
-        <v>1.693071824936896e-10</v>
+        <v>1.693071824936891e-10</v>
       </c>
       <c r="T8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="U8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="V8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="W8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="X8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68384887093257e-10</v>
+        <v>1.683848870932561e-10</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.036792415656523e-10</v>
+        <v>2.036792415656527e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.238853561498757e-10</v>
+        <v>1.238853561498754e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>2.088739849911947e-10</v>
+        <v>2.088739849911938e-10</v>
       </c>
       <c r="E9" t="n">
-        <v>1.406813106896511e-10</v>
+        <v>1.406813106896512e-10</v>
       </c>
       <c r="F9" t="n">
-        <v>1.627546650275634e-10</v>
+        <v>1.627546650275612e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>2.480986155352408e-10</v>
+        <v>2.480986155352357e-10</v>
       </c>
       <c r="H9" t="n">
-        <v>1.351483434859456e-10</v>
+        <v>1.351483434859449e-10</v>
       </c>
       <c r="I9" t="n">
-        <v>1.795326366122287e-10</v>
+        <v>1.795326366122274e-10</v>
       </c>
       <c r="J9" t="n">
-        <v>2.250843728742045e-10</v>
+        <v>2.250843728742048e-10</v>
       </c>
       <c r="K9" t="n">
-        <v>1.775350482638153e-10</v>
+        <v>1.775350482638149e-10</v>
       </c>
       <c r="L9" t="n">
-        <v>2.749843158880921e-10</v>
+        <v>2.749843158880914e-10</v>
       </c>
       <c r="M9" t="n">
-        <v>3.13985627178178e-10</v>
+        <v>3.139856271781754e-10</v>
       </c>
       <c r="N9" t="n">
-        <v>1.217649790211038e-10</v>
+        <v>1.217649790211033e-10</v>
       </c>
       <c r="O9" t="n">
-        <v>1.504481019039751e-10</v>
+        <v>1.504481019039739e-10</v>
       </c>
       <c r="P9" t="n">
-        <v>2.137059193401315e-10</v>
+        <v>2.137059193401385e-10</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.602074356265249e-10</v>
+        <v>1.602074356265244e-10</v>
       </c>
       <c r="R9" t="n">
-        <v>1.517108278886381e-10</v>
+        <v>1.517108278886373e-10</v>
       </c>
       <c r="S9" t="n">
-        <v>2.221971435345345e-10</v>
+        <v>2.221971435345346e-10</v>
       </c>
       <c r="T9" t="n">
-        <v>1.53991200595819e-10</v>
+        <v>1.539912005958183e-10</v>
       </c>
       <c r="U9" t="n">
-        <v>2.976738234111919e-10</v>
+        <v>2.976738234111903e-10</v>
       </c>
       <c r="V9" t="n">
-        <v>2.036541991515022e-10</v>
+        <v>2.036541991515011e-10</v>
       </c>
       <c r="W9" t="n">
-        <v>2.541553446590391e-10</v>
+        <v>2.541553446590378e-10</v>
       </c>
       <c r="X9" t="n">
-        <v>2.712891130250214e-10</v>
+        <v>2.712891130250202e-10</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.722835726143646e-10</v>
+        <v>3.722835726143642e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.961356452988578e-10</v>
+        <v>1.961356452988571e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.59163049381891e-10</v>
+        <v>1.591630493818909e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.471236959001657e-10</v>
+        <v>4.471236959001694e-10</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.721014127582643e-10</v>
+        <v>1.721014127582637e-10</v>
       </c>
       <c r="C10" t="n">
-        <v>2.351565547808252e-10</v>
+        <v>2.351565547808253e-10</v>
       </c>
       <c r="D10" t="n">
-        <v>2.351565547808252e-10</v>
+        <v>2.351565547808253e-10</v>
       </c>
       <c r="E10" t="n">
-        <v>2.015815516625817e-10</v>
+        <v>2.015815516625814e-10</v>
       </c>
       <c r="F10" t="n">
-        <v>1.819246669453376e-10</v>
+        <v>1.819246669453374e-10</v>
       </c>
       <c r="G10" t="n">
-        <v>2.482314492458246e-10</v>
+        <v>2.482314492458242e-10</v>
       </c>
       <c r="H10" t="n">
-        <v>2.351565547808252e-10</v>
+        <v>2.351565547808253e-10</v>
       </c>
       <c r="I10" t="n">
-        <v>2.351565547808252e-10</v>
+        <v>2.351565547808253e-10</v>
       </c>
       <c r="J10" t="n">
-        <v>2.351565547808252e-10</v>
+        <v>2.351565547808253e-10</v>
       </c>
       <c r="K10" t="n">
-        <v>2.351565547808252e-10</v>
+        <v>2.351565547808253e-10</v>
       </c>
       <c r="L10" t="n">
-        <v>2.351565547808252e-10</v>
+        <v>2.351565547808253e-10</v>
       </c>
       <c r="M10" t="n">
         <v>2.351565547808227e-10</v>
       </c>
       <c r="N10" t="n">
-        <v>1.862782708199511e-10</v>
+        <v>1.862782708199507e-10</v>
       </c>
       <c r="O10" t="n">
-        <v>1.997104476596112e-10</v>
+        <v>1.997104476596109e-10</v>
       </c>
       <c r="P10" t="n">
-        <v>1.964178965488672e-10</v>
+        <v>1.964178965488669e-10</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.597096381854164e-10</v>
+        <v>1.597096381854157e-10</v>
       </c>
       <c r="R10" t="n">
-        <v>2.351565547808252e-10</v>
+        <v>2.351565547808253e-10</v>
       </c>
       <c r="S10" t="n">
-        <v>2.351565547808252e-10</v>
+        <v>2.351565547808253e-10</v>
       </c>
       <c r="T10" t="n">
-        <v>2.351565547808252e-10</v>
+        <v>2.351565547808253e-10</v>
       </c>
       <c r="U10" t="n">
-        <v>2.04392609931476e-10</v>
+        <v>2.043926099314757e-10</v>
       </c>
       <c r="V10" t="n">
-        <v>2.179363418532034e-10</v>
+        <v>2.17936341853203e-10</v>
       </c>
       <c r="W10" t="n">
-        <v>2.351689469309355e-10</v>
+        <v>2.351689469309352e-10</v>
       </c>
       <c r="X10" t="n">
-        <v>1.65488767249115e-10</v>
+        <v>1.654887672491148e-10</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.978721086095551e-10</v>
+        <v>2.978721086095541e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.709301311220178e-10</v>
+        <v>1.709301311220172e-10</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.351565547808252e-10</v>
+        <v>2.351565547808253e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.010229232159122e-10</v>
+        <v>3.010229232159123e-10</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="C11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="D11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="E11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="G11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="H11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="I11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="J11" t="n">
-        <v>2.484163934811745e-10</v>
+        <v>2.484163934811742e-10</v>
       </c>
       <c r="K11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="L11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432907e-10</v>
       </c>
       <c r="M11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="N11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="O11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="P11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="R11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="S11" t="n">
-        <v>2.473834673899492e-10</v>
+        <v>2.473834673899512e-10</v>
       </c>
       <c r="T11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="U11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="V11" t="n">
-        <v>2.568461096479456e-10</v>
+        <v>2.568461096479609e-10</v>
       </c>
       <c r="W11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="X11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.469301357432891e-10</v>
+        <v>2.469301357432909e-10</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.642782086310854e-10</v>
+        <v>2.642782086310846e-10</v>
       </c>
       <c r="C12" t="n">
-        <v>2.250574844986739e-10</v>
+        <v>2.250574844986754e-10</v>
       </c>
       <c r="D12" t="n">
-        <v>2.668315571460775e-10</v>
+        <v>2.668315571460819e-10</v>
       </c>
       <c r="E12" t="n">
-        <v>2.333131233375718e-10</v>
+        <v>2.333131233375739e-10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.441627384008461e-10</v>
+        <v>2.441627384008478e-10</v>
       </c>
       <c r="G12" t="n">
-        <v>2.861114606843961e-10</v>
+        <v>2.861114606843957e-10</v>
       </c>
       <c r="H12" t="n">
-        <v>2.305935292333437e-10</v>
+        <v>2.305935292333446e-10</v>
       </c>
       <c r="I12" t="n">
-        <v>2.524095381599354e-10</v>
+        <v>2.524095381599337e-10</v>
       </c>
       <c r="J12" t="n">
-        <v>2.762856328179553e-10</v>
+        <v>2.762856328179569e-10</v>
       </c>
       <c r="K12" t="n">
-        <v>2.514276726807068e-10</v>
+        <v>2.514276726807097e-10</v>
       </c>
       <c r="L12" t="n">
-        <v>2.993264662095855e-10</v>
+        <v>2.993264662095867e-10</v>
       </c>
       <c r="M12" t="n">
-        <v>3.184966026547564e-10</v>
+        <v>3.184966026547582e-10</v>
       </c>
       <c r="N12" t="n">
-        <v>2.240152652109314e-10</v>
+        <v>2.240152652109331e-10</v>
       </c>
       <c r="O12" t="n">
-        <v>2.381137496246597e-10</v>
+        <v>2.381137496246602e-10</v>
       </c>
       <c r="P12" t="n">
-        <v>2.692065757723556e-10</v>
+        <v>2.692065757723587e-10</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.429107103648693e-10</v>
+        <v>2.429107103648698e-10</v>
       </c>
       <c r="R12" t="n">
-        <v>2.387344115618649e-10</v>
+        <v>2.387344115618651e-10</v>
       </c>
       <c r="S12" t="n">
-        <v>2.733802284268145e-10</v>
+        <v>2.733802284268141e-10</v>
       </c>
       <c r="T12" t="n">
-        <v>2.398552727456684e-10</v>
+        <v>2.398552727456697e-10</v>
       </c>
       <c r="U12" t="n">
-        <v>3.104789362344106e-10</v>
+        <v>3.104789362344114e-10</v>
       </c>
       <c r="V12" t="n">
-        <v>2.741818735523096e-10</v>
+        <v>2.741818735522821e-10</v>
       </c>
       <c r="W12" t="n">
-        <v>2.890884970935326e-10</v>
+        <v>2.890884970935322e-10</v>
       </c>
       <c r="X12" t="n">
-        <v>2.975101800198528e-10</v>
+        <v>2.975101800198512e-10</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.471515255667691e-10</v>
+        <v>3.471515255667723e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.605703392046925e-10</v>
+        <v>2.605703392046937e-10</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.423973679630672e-10</v>
+        <v>2.42397367963071e-10</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.839373496199956e-10</v>
+        <v>3.839373496199909e-10</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.487569026324904e-10</v>
+        <v>2.487569026324914e-10</v>
       </c>
       <c r="C13" t="n">
-        <v>2.797501086596268e-10</v>
+        <v>2.797501086596294e-10</v>
       </c>
       <c r="D13" t="n">
-        <v>2.797501086596268e-10</v>
+        <v>2.797501086596294e-10</v>
       </c>
       <c r="E13" t="n">
-        <v>2.632471406917939e-10</v>
+        <v>2.632471406917951e-10</v>
       </c>
       <c r="F13" t="n">
         <v>2.535852819067444e-10</v>
       </c>
       <c r="G13" t="n">
-        <v>2.861767518315953e-10</v>
+        <v>2.861767518315969e-10</v>
       </c>
       <c r="H13" t="n">
-        <v>2.797501086596268e-10</v>
+        <v>2.797501086596294e-10</v>
       </c>
       <c r="I13" t="n">
-        <v>2.797501086596268e-10</v>
+        <v>2.797501086596294e-10</v>
       </c>
       <c r="J13" t="n">
-        <v>2.812363663975131e-10</v>
+        <v>2.812363663975117e-10</v>
       </c>
       <c r="K13" t="n">
-        <v>2.797501086596268e-10</v>
+        <v>2.797501086596294e-10</v>
       </c>
       <c r="L13" t="n">
-        <v>2.797501086596268e-10</v>
+        <v>2.797501086596294e-10</v>
       </c>
       <c r="M13" t="n">
-        <v>2.797501086596255e-10</v>
+        <v>2.797501086596284e-10</v>
       </c>
       <c r="N13" t="n">
-        <v>2.557251889391982e-10</v>
+        <v>2.557251889391957e-10</v>
       </c>
       <c r="O13" t="n">
         <v>2.623274454853107e-10</v>
       </c>
       <c r="P13" t="n">
-        <v>2.607090728727544e-10</v>
+        <v>2.607090728727559e-10</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.426660302617535e-10</v>
+        <v>2.426660302617539e-10</v>
       </c>
       <c r="R13" t="n">
-        <v>2.797501086596268e-10</v>
+        <v>2.797501086596294e-10</v>
       </c>
       <c r="S13" t="n">
-        <v>2.797501086596268e-10</v>
+        <v>2.797501086596294e-10</v>
       </c>
       <c r="T13" t="n">
-        <v>2.797501086596268e-10</v>
+        <v>2.797501086596294e-10</v>
       </c>
       <c r="U13" t="n">
-        <v>2.646288473264559e-10</v>
+        <v>2.646288473264573e-10</v>
       </c>
       <c r="V13" t="n">
-        <v>2.812019099373374e-10</v>
+        <v>2.812019099373297e-10</v>
       </c>
       <c r="W13" t="n">
-        <v>2.797561997165838e-10</v>
+        <v>2.797561997165832e-10</v>
       </c>
       <c r="X13" t="n">
         <v>2.455066191809652e-10</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.105763984525246e-10</v>
+        <v>3.105763984525228e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.48181187918296e-10</v>
+        <v>2.481811879182954e-10</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.797501086596268e-10</v>
+        <v>2.797501086596294e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.121251039682965e-10</v>
+        <v>3.121251039682983e-10</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="C14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="D14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="E14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="F14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="G14" t="n">
-        <v>1.198142751502411e-10</v>
+        <v>1.198142751502412e-10</v>
       </c>
       <c r="H14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="I14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="J14" t="n">
-        <v>1.199181470524657e-10</v>
+        <v>1.199181470524656e-10</v>
       </c>
       <c r="K14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="L14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="M14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="N14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="O14" t="n">
-        <v>1.198142751502411e-10</v>
+        <v>1.198142751502412e-10</v>
       </c>
       <c r="P14" t="n">
-        <v>1.198142751502411e-10</v>
+        <v>1.198142751502412e-10</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="R14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="S14" t="n">
-        <v>1.233508733609359e-10</v>
+        <v>1.23350873360936e-10</v>
       </c>
       <c r="T14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="U14" t="n">
-        <v>1.19814275150241e-10</v>
+        <v>1.198142751502412e-10</v>
       </c>
       <c r="V14" t="n">
-        <v>1.199553807909022e-10</v>
+        <v>1.199553807909024e-10</v>
       </c>
       <c r="W14" t="n">
-        <v>1.198142751502411e-10</v>
+        <v>1.198142751502412e-10</v>
       </c>
       <c r="X14" t="n">
-        <v>1.198142751502411e-10</v>
+        <v>1.198142751502412e-10</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.228975417142758e-10</v>
+        <v>1.228975417142754e-10</v>
       </c>
     </row>
     <row r="15">
@@ -7634,76 +7634,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.402456146020719e-10</v>
+        <v>1.402456146020717e-10</v>
       </c>
       <c r="C15" t="n">
-        <v>1.010248904696606e-10</v>
+        <v>1.010248904696604e-10</v>
       </c>
       <c r="D15" t="n">
-        <v>1.427989631170645e-10</v>
+        <v>1.427989631170641e-10</v>
       </c>
       <c r="E15" t="n">
         <v>1.092805293085586e-10</v>
       </c>
       <c r="F15" t="n">
-        <v>1.201301443718331e-10</v>
+        <v>1.201301443718328e-10</v>
       </c>
       <c r="G15" t="n">
-        <v>1.589956000913474e-10</v>
+        <v>1.589956000913434e-10</v>
       </c>
       <c r="H15" t="n">
-        <v>1.065609352043301e-10</v>
+        <v>1.0656093520433e-10</v>
       </c>
       <c r="I15" t="n">
-        <v>1.283769441309221e-10</v>
+        <v>1.283769441309218e-10</v>
       </c>
       <c r="J15" t="n">
-        <v>1.477873863892487e-10</v>
+        <v>1.477873863892481e-10</v>
       </c>
       <c r="K15" t="n">
-        <v>1.273950786516938e-10</v>
+        <v>1.273950786516936e-10</v>
       </c>
       <c r="L15" t="n">
-        <v>1.752938721805726e-10</v>
+        <v>1.752938721805722e-10</v>
       </c>
       <c r="M15" t="n">
-        <v>1.944640086257434e-10</v>
+        <v>1.944640086257459e-10</v>
       </c>
       <c r="N15" t="n">
-        <v>9.998267118191818e-11</v>
+        <v>9.998267118191785e-11</v>
       </c>
       <c r="O15" t="n">
-        <v>1.109978890316116e-10</v>
+        <v>1.10997889031611e-10</v>
       </c>
       <c r="P15" t="n">
-        <v>1.420907151793077e-10</v>
+        <v>1.420907151793052e-10</v>
       </c>
       <c r="Q15" t="n">
         <v>1.18878116335856e-10</v>
       </c>
       <c r="R15" t="n">
-        <v>1.147018175328518e-10</v>
+        <v>1.147018175328515e-10</v>
       </c>
       <c r="S15" t="n">
-        <v>1.493476343978013e-10</v>
+        <v>1.493476343978018e-10</v>
       </c>
       <c r="T15" t="n">
-        <v>1.158226787166555e-10</v>
+        <v>1.158226787166548e-10</v>
       </c>
       <c r="U15" t="n">
-        <v>1.833630756413627e-10</v>
+        <v>1.83363075641362e-10</v>
       </c>
       <c r="V15" t="n">
-        <v>1.372911446952236e-10</v>
+        <v>1.372911446952232e-10</v>
       </c>
       <c r="W15" t="n">
-        <v>1.619726365004846e-10</v>
+        <v>1.619726365004841e-10</v>
       </c>
       <c r="X15" t="n">
-        <v>1.70394319426805e-10</v>
+        <v>1.703943194268037e-10</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.231189315377559e-10</v>
+        <v>2.231189315377575e-10</v>
       </c>
       <c r="Z15" t="n">
         <v>1.365377451756793e-10</v>
@@ -7712,7 +7712,7 @@
         <v>1.183647739340537e-10</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.599047555909821e-10</v>
+        <v>2.599047555909847e-10</v>
       </c>
     </row>
     <row r="16">
@@ -7722,85 +7722,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.247243086034772e-10</v>
+        <v>1.24724308603477e-10</v>
       </c>
       <c r="C16" t="n">
-        <v>1.557175146306137e-10</v>
+        <v>1.557175146306131e-10</v>
       </c>
       <c r="D16" t="n">
-        <v>1.557175146306137e-10</v>
+        <v>1.557175146306131e-10</v>
       </c>
       <c r="E16" t="n">
-        <v>1.392145466627808e-10</v>
+        <v>1.392145466627805e-10</v>
       </c>
       <c r="F16" t="n">
-        <v>1.295526878777314e-10</v>
+        <v>1.295526878777311e-10</v>
       </c>
       <c r="G16" t="n">
         <v>1.590608912385472e-10</v>
       </c>
       <c r="H16" t="n">
-        <v>1.557175146306137e-10</v>
+        <v>1.557175146306131e-10</v>
       </c>
       <c r="I16" t="n">
-        <v>1.557175146306137e-10</v>
+        <v>1.557175146306131e-10</v>
       </c>
       <c r="J16" t="n">
-        <v>1.527381199688037e-10</v>
+        <v>1.527381199688038e-10</v>
       </c>
       <c r="K16" t="n">
-        <v>1.557175146306137e-10</v>
+        <v>1.557175146306131e-10</v>
       </c>
       <c r="L16" t="n">
-        <v>1.557175146306137e-10</v>
+        <v>1.557175146306131e-10</v>
       </c>
       <c r="M16" t="n">
-        <v>1.557175146306124e-10</v>
+        <v>1.55717514630612e-10</v>
       </c>
       <c r="N16" t="n">
-        <v>1.316925949101851e-10</v>
+        <v>1.316925949101847e-10</v>
       </c>
       <c r="O16" t="n">
-        <v>1.352115848922627e-10</v>
+        <v>1.352115848922631e-10</v>
       </c>
       <c r="P16" t="n">
-        <v>1.335932122797065e-10</v>
+        <v>1.335932122797063e-10</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.186334362327404e-10</v>
+        <v>1.186334362327405e-10</v>
       </c>
       <c r="R16" t="n">
-        <v>1.557175146306137e-10</v>
+        <v>1.557175146306131e-10</v>
       </c>
       <c r="S16" t="n">
-        <v>1.557175146306137e-10</v>
+        <v>1.557175146306131e-10</v>
       </c>
       <c r="T16" t="n">
-        <v>1.557175146306137e-10</v>
+        <v>1.557175146306131e-10</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37512986733408e-10</v>
+        <v>1.375129867334076e-10</v>
       </c>
       <c r="V16" t="n">
         <v>1.44311181080272e-10</v>
       </c>
       <c r="W16" t="n">
-        <v>1.526403391235358e-10</v>
+        <v>1.526403391235359e-10</v>
       </c>
       <c r="X16" t="n">
         <v>1.183907585879174e-10</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.865438044235112e-10</v>
+        <v>1.865438044235111e-10</v>
       </c>
       <c r="Z16" t="n">
         <v>1.241485938892831e-10</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.557175146306137e-10</v>
+        <v>1.557175146306131e-10</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.880925099392836e-10</v>
+        <v>1.88092509939283e-10</v>
       </c>
     </row>
   </sheetData>
@@ -9451,7 +9451,7 @@
         <v>1.272884560678104e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.733216017311398e-11</v>
+        <v>6.733216017311399e-11</v>
       </c>
       <c r="F2" t="n">
         <v>1.102744561151809e-10</v>
@@ -9478,7 +9478,7 @@
         <v>1.060865921272884e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>9.864261224785824e-11</v>
+        <v>9.864261224785822e-11</v>
       </c>
       <c r="O2" t="n">
         <v>8.795983942343075e-11</v>
@@ -9533,7 +9533,7 @@
         <v>1.142160196502343e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>1.691860430215721e-10</v>
+        <v>1.691860430215722e-10</v>
       </c>
       <c r="D3" t="n">
         <v>1.679132741506017e-10</v>
@@ -9627,7 +9627,7 @@
         <v>2.040025905959939e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.793738056393038e-10</v>
+        <v>1.793738056393039e-10</v>
       </c>
       <c r="F4" t="n">
         <v>1.969526796743424e-10</v>
@@ -9806,7 +9806,7 @@
         <v>4.414583835109933e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>6.172471238613665e-11</v>
+        <v>6.172471238613663e-11</v>
       </c>
       <c r="G6" t="n">
         <v>5.379768116440763e-11</v>
@@ -9839,7 +9839,7 @@
         <v>4.8439539055357e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.66180414151245e-11</v>
+        <v>5.661804141512451e-11</v>
       </c>
       <c r="R6" t="n">
         <v>6.462613970281951e-11</v>
@@ -9857,7 +9857,7 @@
         <v>5.041341719822265e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>7.754669534648142e-11</v>
+        <v>7.754669534648141e-11</v>
       </c>
       <c r="X6" t="n">
         <v>7.567601768188366e-11</v>
@@ -9882,10 +9882,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.400987373787856e-11</v>
+        <v>6.400987373787857e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>8.485466132923582e-11</v>
+        <v>8.485466132923579e-11</v>
       </c>
       <c r="D7" t="n">
         <v>8.35818924582652e-11</v>
@@ -10158,7 +10158,7 @@
         <v>1.873364930792219e-10</v>
       </c>
       <c r="F10" t="n">
-        <v>1.693463457226043e-10</v>
+        <v>1.693463457226044e-10</v>
       </c>
       <c r="G10" t="n">
         <v>2.300308743993976e-10</v>
@@ -10188,7 +10188,7 @@
         <v>1.856240428499663e-10</v>
       </c>
       <c r="P10" t="n">
-        <v>1.826106721906923e-10</v>
+        <v>1.826106721906924e-10</v>
       </c>
       <c r="Q10" t="n">
         <v>1.490149632749316e-10</v>
@@ -10443,7 +10443,7 @@
         <v>2.618291990463122e-10</v>
       </c>
       <c r="M13" t="n">
-        <v>2.618291990463097e-10</v>
+        <v>2.618291990463096e-10</v>
       </c>
       <c r="N13" t="n">
         <v>2.398413890644073e-10</v>
@@ -10616,7 +10616,7 @@
         <v>1.147177077918811e-10</v>
       </c>
       <c r="L15" t="n">
-        <v>1.175303352864484e-10</v>
+        <v>1.175303352864483e-10</v>
       </c>
       <c r="M15" t="n">
         <v>1.141497498222985e-10</v>
@@ -10713,7 +10713,7 @@
         <v>1.235625655203935e-10</v>
       </c>
       <c r="O16" t="n">
-        <v>1.265941374404214e-10</v>
+        <v>1.265941374404213e-10</v>
       </c>
       <c r="P16" t="n">
         <v>1.251129891203433e-10</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide human toxicity carcinogenic results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide human toxicity carcinogenic results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.110082348664e-10</v>
+        <v>2.110082348663979e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>8.897371995158038e-11</v>
+        <v>8.897371995158068e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.633154310523399e-10</v>
+        <v>1.633154310523397e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>1.013179188172623e-10</v>
+        <v>1.013179188172618e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>1.27135463376874e-10</v>
+        <v>1.271354633768741e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>2.235535472423125e-10</v>
+        <v>2.235535472423121e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>1.245313376644731e-10</v>
+        <v>1.245313376644711e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>1.730497474484547e-10</v>
+        <v>1.730497474484597e-10</v>
       </c>
       <c r="J2" t="n">
         <v>1.913218837758375e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>2.436897037226098e-10</v>
+        <v>2.436897037226096e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>2.749787483858338e-10</v>
+        <v>2.74978748385836e-10</v>
       </c>
       <c r="M2" t="n">
         <v>3.297397696290092e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>1.808787710858764e-10</v>
+        <v>1.808787710858742e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>1.511742342171697e-10</v>
+        <v>1.511742342171702e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>1.655475834387349e-10</v>
+        <v>1.65547583438733e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.164822650725577e-10</v>
+        <v>1.16482265072558e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>1.187157541731598e-10</v>
+        <v>1.187157541731597e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>1.782798417727296e-10</v>
+        <v>1.7827984177273e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>1.48457638919635e-10</v>
+        <v>1.484576389196351e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>3.125568357725492e-10</v>
+        <v>3.125568357725473e-10</v>
       </c>
       <c r="V2" t="n">
         <v>1.329039203957393e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>1.841259451388194e-10</v>
+        <v>1.841259451388197e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>1.550131274027004e-10</v>
+        <v>1.55013127402699e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.708317498906685e-10</v>
+        <v>1.708317498906657e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.6412015382287e-10</v>
+        <v>1.641201538228719e-10</v>
       </c>
       <c r="AA2" t="n">
         <v>1.25446188556101e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.396348830770854e-10</v>
+        <v>4.396348830770868e-10</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.328104091022635e-10</v>
+        <v>1.328104091022694e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>1.966094740918036e-10</v>
+        <v>1.966094740918034e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>1.95432374523224e-10</v>
+        <v>1.954323745232201e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.570800712846821e-10</v>
+        <v>1.570800712846818e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.409341632477166e-10</v>
+        <v>1.409341632477164e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>2.084174469980602e-10</v>
+        <v>2.084174469980585e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.95432374523224e-10</v>
+        <v>1.954323745232201e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.95432374523224e-10</v>
+        <v>1.954323745232201e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.931595973363689e-10</v>
+        <v>1.931595973363676e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.95432374523224e-10</v>
+        <v>1.954323745232201e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.95432374523224e-10</v>
+        <v>1.954323745232201e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>1.932260956953625e-10</v>
+        <v>1.932260956953624e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>1.46889874897711e-10</v>
+        <v>1.468898748977134e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.602297752869805e-10</v>
+        <v>1.602297752869722e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.569598433638743e-10</v>
+        <v>1.569598433638696e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.205037636181054e-10</v>
+        <v>1.205037636181039e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.95432374523224e-10</v>
+        <v>1.954323745232201e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.95432374523224e-10</v>
+        <v>1.954323745232201e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95432374523224e-10</v>
+        <v>1.954323745232201e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.648662216603688e-10</v>
+        <v>1.64866221660378e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>1.728916250966258e-10</v>
+        <v>1.72891625096626e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.954446815427439e-10</v>
+        <v>1.954446815427402e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>1.262431911861667e-10</v>
+        <v>1.262431911861703e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.576939039471586e-10</v>
+        <v>2.576939039471595e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.316471739436822e-10</v>
+        <v>1.316471739436828e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95432374523224e-10</v>
+        <v>1.954323745232201e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.610907658074331e-10</v>
+        <v>2.610907658074327e-10</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.50855263488098e-10</v>
+        <v>2.508552634880964e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>2.07123176401303e-10</v>
+        <v>2.071231764013008e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.334717965350508e-10</v>
+        <v>2.334717965350493e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>2.076918178382052e-10</v>
+        <v>2.076918178382031e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.192474577112263e-10</v>
+        <v>2.192474577112247e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>2.554278825346225e-10</v>
+        <v>2.554278825346219e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>2.193354499209912e-10</v>
+        <v>2.193354499209889e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>2.370198405553203e-10</v>
+        <v>2.370198405553172e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>2.438469303467461e-10</v>
+        <v>2.438469303467474e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>2.62767275121004e-10</v>
+        <v>2.627672751210023e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>2.741717644862369e-10</v>
+        <v>2.741717644862356e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>2.927293975904575e-10</v>
+        <v>2.927293975904551e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>2.398734277381239e-10</v>
+        <v>2.398734277381299e-10</v>
       </c>
       <c r="O4" t="n">
         <v>2.290464728577618e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34285389868635e-10</v>
+        <v>2.342853898686334e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.164016574782204e-10</v>
+        <v>2.164016574782189e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.17215738028437e-10</v>
+        <v>2.172157380284353e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38926148521651e-10</v>
+        <v>2.389261485216488e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>2.280563057716834e-10</v>
+        <v>2.280563057716823e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>2.878685360745132e-10</v>
+        <v>2.878685360745117e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>2.296916676071919e-10</v>
+        <v>2.29691667607192e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>2.41056984550178e-10</v>
+        <v>2.410569845501765e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>2.304457043453289e-10</v>
+        <v>2.304457043453246e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.362114064905497e-10</v>
+        <v>2.362114064905427e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.337651085353772e-10</v>
+        <v>2.337651085353762e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.196689023282685e-10</v>
+        <v>2.196689023282667e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.343423823576141e-10</v>
+        <v>3.343423823576126e-10</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.223530742423008e-10</v>
+        <v>2.223530742422983e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>2.463551448625764e-10</v>
+        <v>2.463551448625743e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.451780452939971e-10</v>
+        <v>2.451780452939982e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.280164676203262e-10</v>
+        <v>2.280164676203238e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.242769217816341e-10</v>
+        <v>2.242769217816322e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.499109517326555e-10</v>
+        <v>2.499109517326525e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>2.451780452939971e-10</v>
+        <v>2.451780452939982e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.451780452939971e-10</v>
+        <v>2.451780452939982e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>2.445167553600374e-10</v>
+        <v>2.44516755360039e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>2.451780452939971e-10</v>
+        <v>2.451780452939982e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>2.451780452939971e-10</v>
+        <v>2.451780452939982e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.429717664661361e-10</v>
+        <v>2.429717664661338e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>2.274848741953066e-10</v>
+        <v>2.274848741953017e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.323471112421767e-10</v>
+        <v>2.323471112421733e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>2.311552594536838e-10</v>
+        <v>2.311552594536778e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.178674464752525e-10</v>
+        <v>2.178674464752564e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>2.451780452939971e-10</v>
+        <v>2.451780452939982e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>2.451780452939971e-10</v>
+        <v>2.451780452939982e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.451780452939971e-10</v>
+        <v>2.451780452939982e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>2.340370415013747e-10</v>
+        <v>2.340370415013735e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.442667164113295e-10</v>
+        <v>2.442667164113294e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>2.451825310580958e-10</v>
+        <v>2.451825310580946e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>2.199594004280498e-10</v>
+        <v>2.199594004280434e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.678716416572303e-10</v>
+        <v>2.678716416572258e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.219290886863952e-10</v>
+        <v>2.219290886863947e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.451780452939971e-10</v>
+        <v>2.451780452939982e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.692651481837018e-10</v>
+        <v>2.692651481836998e-10</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.023263739495436e-10</v>
+        <v>1.023263739495439e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.859428686274891e-11</v>
+        <v>5.859428686274896e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>8.494290699649695e-11</v>
+        <v>8.494290699649658e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>5.916292829965069e-11</v>
+        <v>5.916292829965057e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>7.07185681726725e-11</v>
+        <v>7.071856817267235e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>1.032510991784223e-10</v>
+        <v>1.032510991784232e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>7.080656038243707e-11</v>
+        <v>7.08065603824365e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>8.849095101676633e-11</v>
+        <v>8.849095101676501e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>9.018185794349523e-11</v>
+        <v>9.018185794349407e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>1.142383855824496e-10</v>
+        <v>1.142383855824509e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.256428749476822e-10</v>
+        <v>1.256428749476838e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.442005080519037e-10</v>
+        <v>1.442005080519031e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>9.134453819956932e-11</v>
+        <v>9.134453819957654e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>7.686968950156116e-11</v>
+        <v>7.686968950156339e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>8.210860651243433e-11</v>
+        <v>8.210860651243483e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.787276793966644e-11</v>
+        <v>6.787276793966763e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>6.868684848988235e-11</v>
+        <v>6.868684848988292e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>9.039725898309682e-11</v>
+        <v>9.039725898309702e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>7.952741623312939e-11</v>
+        <v>7.952741623312983e-11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.356917527183126e-10</v>
+        <v>1.356917527183136e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>6.693113811895045e-11</v>
+        <v>6.693113811895043e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>8.888020119397787e-11</v>
+        <v>8.888020119397949e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>7.826892098912857e-11</v>
+        <v>7.826892098912734e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.768251695199571e-11</v>
+        <v>8.768251695198965e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.523621899682298e-11</v>
+        <v>8.523621899682375e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.114001278971373e-11</v>
+        <v>7.114001278971497e-11</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.858134928190603e-10</v>
+        <v>1.858134928190605e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1026,82 +1026,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.382418470374687e-11</v>
+        <v>7.382418470374636e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>9.782625532402226e-11</v>
+        <v>9.782625532402237e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>9.664915575544271e-11</v>
+        <v>9.664915575544555e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>7.948757808177168e-11</v>
+        <v>7.948757808177177e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>7.574803224307982e-11</v>
+        <v>7.574803224307978e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>9.773416837645539e-11</v>
+        <v>9.773416837645484e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>9.664915575544271e-11</v>
+        <v>9.664915575544555e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>9.664915575544271e-11</v>
+        <v>9.664915575544555e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>9.085168295678662e-11</v>
+        <v>9.085168295678888e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>9.664915575544271e-11</v>
+        <v>9.664915575544555e-11</v>
       </c>
       <c r="L7" t="n">
-        <v>9.664915575544271e-11</v>
+        <v>9.664915575544555e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>9.444287692758131e-11</v>
+        <v>9.444287692758123e-11</v>
       </c>
       <c r="N7" t="n">
-        <v>7.895598465675273e-11</v>
+        <v>7.895598465674973e-11</v>
       </c>
       <c r="O7" t="n">
-        <v>8.017032788597622e-11</v>
+        <v>8.017032788597473e-11</v>
       </c>
       <c r="P7" t="n">
-        <v>7.89784760974832e-11</v>
+        <v>7.897847609747891e-11</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.933855693669851e-11</v>
+        <v>6.933855693670363e-11</v>
       </c>
       <c r="R7" t="n">
-        <v>9.664915575544271e-11</v>
+        <v>9.664915575544555e-11</v>
       </c>
       <c r="S7" t="n">
-        <v>9.664915575544271e-11</v>
+        <v>9.664915575544555e-11</v>
       </c>
       <c r="T7" t="n">
-        <v>9.664915575544271e-11</v>
+        <v>9.664915575544555e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>8.186025814517428e-11</v>
+        <v>8.186025814517593e-11</v>
       </c>
       <c r="V7" t="n">
-        <v>8.150618692308806e-11</v>
+        <v>8.150618692308793e-11</v>
       </c>
       <c r="W7" t="n">
-        <v>9.300574770189507e-11</v>
+        <v>9.300574770189681e-11</v>
       </c>
       <c r="X7" t="n">
-        <v>6.778261707184948e-11</v>
+        <v>6.778261707184467e-11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.193427521186762e-10</v>
+        <v>1.193427521186739e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.340019914784075e-11</v>
+        <v>7.340019914784209e-11</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.664915575544271e-11</v>
+        <v>9.664915575544555e-11</v>
       </c>
       <c r="AB7" t="n">
         <v>1.207362586451477e-10</v>
@@ -1270,82 +1270,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.67835033328319e-11</v>
+        <v>9.678350333279569e-11</v>
       </c>
       <c r="C2" t="n">
-        <v>9.097240832099556e-11</v>
+        <v>9.097240832099571e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.158197591183014e-10</v>
+        <v>1.158197591182621e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>7.238171431412581e-11</v>
+        <v>7.238171431412573e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.057644724247145e-10</v>
+        <v>1.057644724247143e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>1.122667841084755e-10</v>
+        <v>1.122667841084434e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>1.037277990869808e-10</v>
+        <v>1.037277990869449e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>1.178005830558328e-10</v>
+        <v>1.178005830557981e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>1.107000973917647e-10</v>
+        <v>1.107000973917525e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.17709637559809e-10</v>
+        <v>1.17709637559773e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>1.11149231014557e-10</v>
+        <v>1.111492310145053e-10</v>
       </c>
       <c r="M2" t="n">
         <v>1.065629037243482e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>9.26035560904299e-11</v>
+        <v>9.260355609045414e-11</v>
       </c>
       <c r="O2" t="n">
-        <v>8.100471782617368e-11</v>
+        <v>8.10047178261309e-11</v>
       </c>
       <c r="P2" t="n">
-        <v>8.581747173347099e-11</v>
+        <v>8.581747173347233e-11</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.006521710677593e-10</v>
+        <v>1.006521710677249e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>1.289660719320601e-10</v>
+        <v>1.289660719320271e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>1.058983054399291e-10</v>
+        <v>1.058983054398987e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>9.488473877583777e-11</v>
+        <v>9.48847387758217e-11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.148865933782067e-10</v>
+        <v>1.148865933781716e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>1.043051851766711e-10</v>
+        <v>1.043051851766709e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>2.355889087434732e-10</v>
+        <v>2.355889087434436e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>1.691652331452538e-10</v>
+        <v>1.691652331452174e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.773629016498234e-10</v>
+        <v>1.773629016497873e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.092934800183572e-10</v>
+        <v>1.09293480018324e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.166566646907606e-10</v>
+        <v>1.166566646907153e-10</v>
       </c>
       <c r="AB2" t="n">
         <v>1.331954148349795e-10</v>
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.183124922327133e-10</v>
+        <v>1.183124922326703e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>1.750799130565065e-10</v>
+        <v>1.750799130565067e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>1.737869332374537e-10</v>
+        <v>1.737869332374542e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.398180016326606e-10</v>
+        <v>1.398180016326603e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.255807132168899e-10</v>
+        <v>1.255807132168896e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>1.852899199626616e-10</v>
+        <v>1.852899199626534e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.737869332374537e-10</v>
+        <v>1.737869332374542e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.737869332374537e-10</v>
+        <v>1.737869332374542e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.717561745162409e-10</v>
+        <v>1.717561745162143e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.737869332374537e-10</v>
+        <v>1.737869332374542e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.737869332374537e-10</v>
+        <v>1.737869332374542e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>1.713671201720716e-10</v>
+        <v>1.713671201720709e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>1.307849607887294e-10</v>
+        <v>1.307849607887001e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.426022762010665e-10</v>
+        <v>1.426022762010388e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.397055666467716e-10</v>
+        <v>1.397055666467191e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.074104984312012e-10</v>
+        <v>1.074104984311862e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.737869332374537e-10</v>
+        <v>1.737869332374542e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.737869332374537e-10</v>
+        <v>1.737869332374542e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>1.737869332374537e-10</v>
+        <v>1.737869332374542e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.467209694497905e-10</v>
+        <v>1.467209694497757e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>1.538434854245473e-10</v>
+        <v>1.53843485424547e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.737978355614184e-10</v>
+        <v>1.737978355613944e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>1.124948411828402e-10</v>
+        <v>1.124948411827865e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.289616480793357e-10</v>
+        <v>2.289616480793261e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.172820260099008e-10</v>
+        <v>1.17282026009866e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.737869332374537e-10</v>
+        <v>1.737869332374542e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.311314797840847e-10</v>
+        <v>2.311314797840845e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.95658319425997e-10</v>
+        <v>1.956583194259632e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.943619473894224e-10</v>
+        <v>1.943619473894275e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.025968111247993e-10</v>
+        <v>2.025968111247616e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.839485647472219e-10</v>
+        <v>1.83948564747224e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.980585531915592e-10</v>
+        <v>1.980585531915623e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>2.013017934548585e-10</v>
+        <v>2.013017934548112e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.981894336843482e-10</v>
+        <v>1.981894336843123e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>2.033187981900203e-10</v>
+        <v>2.033187981899869e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>2.011553726149559e-10</v>
+        <v>2.011553726149543e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>2.032856496246567e-10</v>
+        <v>2.032856496246218e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>2.008944584750804e-10</v>
+        <v>2.008944584750496e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>1.976849764152367e-10</v>
+        <v>1.976849764152372e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.94134777739563e-10</v>
+        <v>1.94134777739549e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>1.899071373926734e-10</v>
+        <v>1.899071373926393e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>1.916613296776494e-10</v>
+        <v>1.916613296776537e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.970684033871871e-10</v>
+        <v>1.970684033871547e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.073884877736157e-10</v>
+        <v>2.073884877735797e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>1.98980557762627e-10</v>
+        <v>1.989805577625917e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>1.949662420413767e-10</v>
+        <v>1.94966242041365e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>2.022566831703195e-10</v>
+        <v>2.022566831702864e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>2.067972760999241e-10</v>
+        <v>2.067972760999251e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>2.462512597628185e-10</v>
+        <v>2.462512597627816e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>2.220406099934375e-10</v>
+        <v>2.220406099934069e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.250285639014724e-10</v>
+        <v>2.250285639014407e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.002180590282923e-10</v>
+        <v>2.002180590282746e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.029018533785041e-10</v>
+        <v>2.02901853378481e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.085467273685293e-10</v>
+        <v>2.085467273685317e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.035053830738222e-10</v>
+        <v>2.035053830738156e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>2.250181452253353e-10</v>
+        <v>2.250181452253366e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.237251654062792e-10</v>
+        <v>2.237251654062836e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.085282995979652e-10</v>
+        <v>2.085282995979638e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.052813402662589e-10</v>
+        <v>2.052813402662622e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.279178689927457e-10</v>
+        <v>2.279178689927291e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>2.237251654062792e-10</v>
+        <v>2.237251654062836e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.237251654062792e-10</v>
+        <v>2.237251654062836e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>2.234095957701666e-10</v>
+        <v>2.234095957701652e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>2.237251654062792e-10</v>
+        <v>2.237251654062836e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>2.237251654062792e-10</v>
+        <v>2.237251654062836e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.213053523409028e-10</v>
+        <v>2.213053523409036e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>2.080514514033897e-10</v>
+        <v>2.080514514033681e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.123587241052706e-10</v>
+        <v>2.123587241052408e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>2.113029074876193e-10</v>
+        <v>2.113029074875733e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.995317343508615e-10</v>
+        <v>1.995317343508496e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>2.237251654062792e-10</v>
+        <v>2.237251654062836e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>2.237251654062792e-10</v>
+        <v>2.237251654062836e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.237251654062792e-10</v>
+        <v>2.237251654062836e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>2.138599394302675e-10</v>
+        <v>2.138599394302679e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.24853404832184e-10</v>
+        <v>2.248534048321853e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>2.237291391753513e-10</v>
+        <v>2.237291391753393e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>2.013849175804755e-10</v>
+        <v>2.013849175804393e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.438357010719674e-10</v>
+        <v>2.438357010719353e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.031297902359551e-10</v>
+        <v>2.031297902359487e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.237251654062792e-10</v>
+        <v>2.237251654062836e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.442432730191404e-10</v>
+        <v>2.442432730191431e-10</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.851230071141358e-11</v>
+        <v>5.851230071137235e-11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.721592867484423e-11</v>
+        <v>5.721592867484415e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>6.545079241021524e-11</v>
+        <v>6.54507924101822e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>4.680254603264059e-11</v>
+        <v>4.680254603264063e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>6.091253447697863e-11</v>
+        <v>6.091253447697866e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>6.062369590559054e-11</v>
+        <v>6.062369590554534e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>6.10434149697633e-11</v>
+        <v>6.104341496972161e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>6.617277947543789e-11</v>
+        <v>6.617277947539715e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>5.88806149094646e-11</v>
+        <v>5.888061490945865e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>6.613963091007184e-11</v>
+        <v>6.613963091003143e-11</v>
       </c>
       <c r="L6" t="n">
-        <v>6.374843976049814e-11</v>
+        <v>6.374843976047945e-11</v>
       </c>
       <c r="M6" t="n">
-        <v>6.053895770065437e-11</v>
+        <v>6.053895770065389e-11</v>
       </c>
       <c r="N6" t="n">
-        <v>5.698875902498136e-11</v>
+        <v>5.698875902495758e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>4.922903984340835e-11</v>
+        <v>4.922903984337407e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>5.098323212838496e-11</v>
+        <v>5.098323212838867e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.992238467260479e-11</v>
+        <v>5.99223846725635e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>7.024246905903154e-11</v>
+        <v>7.024246905898976e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>6.183453904804517e-11</v>
+        <v>6.183453904800199e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>5.782022332679328e-11</v>
+        <v>5.782022332677484e-11</v>
       </c>
       <c r="U6" t="n">
-        <v>6.157858562105509e-11</v>
+        <v>6.157858562102142e-11</v>
       </c>
       <c r="V6" t="n">
-        <v>5.483633677429843e-11</v>
+        <v>5.483633677429819e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.055731622135516e-10</v>
+        <v>1.055731622135169e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>8.136251244417419e-11</v>
+        <v>8.136251244414191e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.788254518688912e-11</v>
+        <v>8.788254518685132e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.307204031370921e-11</v>
+        <v>6.307204031368398e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.575583466391881e-11</v>
+        <v>6.575583466390364e-11</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.140070865394813e-11</v>
+        <v>7.140070865394812e-11</v>
       </c>
     </row>
     <row r="7">
@@ -1710,82 +1710,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.635936435923833e-11</v>
+        <v>6.635936435922321e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>8.787212651075348e-11</v>
+        <v>8.787212651075361e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>8.657914669169897e-11</v>
+        <v>8.657914669169361e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>7.138228088338074e-11</v>
+        <v>7.138228088338058e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8135321551679e-11</v>
+        <v>6.813532155167905e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>8.723977144348081e-11</v>
+        <v>8.723977144346508e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>8.657914669169897e-11</v>
+        <v>8.657914669169361e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>8.657914669169897e-11</v>
+        <v>8.657914669169361e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>8.113483806469956e-11</v>
+        <v>8.113483806467112e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>8.657914669169897e-11</v>
+        <v>8.657914669169361e-11</v>
       </c>
       <c r="L7" t="n">
-        <v>8.657914669169897e-11</v>
+        <v>8.657914669169361e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>8.415933362632034e-11</v>
+        <v>8.415933362632e-11</v>
       </c>
       <c r="N7" t="n">
-        <v>7.090543268880753e-11</v>
+        <v>7.090543268877678e-11</v>
       </c>
       <c r="O7" t="n">
-        <v>7.168062655600614e-11</v>
+        <v>7.168062655597641e-11</v>
       </c>
       <c r="P7" t="n">
-        <v>7.062480993835234e-11</v>
+        <v>7.062480993830764e-11</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.238571563627911e-11</v>
+        <v>6.238571563625693e-11</v>
       </c>
       <c r="R7" t="n">
-        <v>8.657914669169897e-11</v>
+        <v>8.657914669169361e-11</v>
       </c>
       <c r="S7" t="n">
-        <v>8.657914669169897e-11</v>
+        <v>8.657914669169361e-11</v>
       </c>
       <c r="T7" t="n">
-        <v>8.657914669169897e-11</v>
+        <v>8.657914669169361e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>7.31818418810022e-11</v>
+        <v>7.318184188100233e-11</v>
       </c>
       <c r="V7" t="n">
-        <v>7.289246550655864e-11</v>
+        <v>7.289246550655861e-11</v>
       </c>
       <c r="W7" t="n">
-        <v>8.305104162608687e-11</v>
+        <v>8.305104162607459e-11</v>
       </c>
       <c r="X7" t="n">
-        <v>6.070682003121277e-11</v>
+        <v>6.070682003117422e-11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.066896823573864e-10</v>
+        <v>1.066896823573408e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.598377152137577e-11</v>
+        <v>6.598377152135821e-11</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.657914669169897e-11</v>
+        <v>8.657914669169361e-11</v>
       </c>
       <c r="AB7" t="n">
         <v>1.070972543045603e-10</v>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.881780928202496e-10</v>
+        <v>1.881780928202892e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>8.948303173316158e-11</v>
+        <v>8.94830317331679e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.572175049045453e-10</v>
+        <v>1.572175049045521e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>9.603123181332864e-11</v>
+        <v>9.603123181334667e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>9.74903294600805e-11</v>
+        <v>9.749032946008214e-11</v>
       </c>
       <c r="G2" t="n">
-        <v>2.190208317862037e-10</v>
+        <v>2.190208317862066e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>9.616201152316003e-11</v>
+        <v>9.616201152316627e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>1.282718014515609e-10</v>
+        <v>1.282718014515651e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>1.84542707832927e-10</v>
+        <v>1.845427078329268e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>2.146221168035922e-10</v>
+        <v>2.146221168035998e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>2.668580932187911e-10</v>
+        <v>2.668580932189242e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>3.056523170211987e-10</v>
+        <v>3.05652317021204e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>1.204698624300184e-10</v>
+        <v>1.204698624300239e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>1.275895890580929e-10</v>
+        <v>1.275895890580993e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>1.776926544433863e-10</v>
+        <v>1.776926544433923e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.040607131458076e-10</v>
+        <v>1.040607131458115e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>1.008391067769916e-10</v>
+        <v>1.00839106776998e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>1.790944500122069e-10</v>
+        <v>1.790944500122247e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>1.092447919977373e-10</v>
+        <v>1.092447919977432e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>2.779295352075435e-10</v>
+        <v>2.779295352075496e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>1.097677951291398e-10</v>
+        <v>1.09767795129138e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>1.992010346652755e-10</v>
+        <v>1.992010346652816e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>1.672655516644525e-10</v>
+        <v>1.672655516644458e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.640478426139729e-10</v>
+        <v>1.640478426139812e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.476495926289377e-10</v>
+        <v>1.476495926289502e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.107049302369974e-10</v>
+        <v>1.107049302370121e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.277963170118144e-10</v>
+        <v>4.277963170118352e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.288788564955546e-10</v>
+        <v>1.288788564955534e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>1.909354720368866e-10</v>
+        <v>1.909354720368818e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>1.897176400077593e-10</v>
+        <v>1.89717640007761e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.524209978178858e-10</v>
+        <v>1.524209978178862e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.366944337423631e-10</v>
+        <v>1.366944337423636e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>2.023329580974463e-10</v>
+        <v>2.023329580974462e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.897176400077593e-10</v>
+        <v>1.89717640007761e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.897176400077593e-10</v>
+        <v>1.89717640007761e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.874785506062311e-10</v>
+        <v>1.874785506062337e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.897176400077593e-10</v>
+        <v>1.89717640007761e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.897176400077593e-10</v>
+        <v>1.89717640007761e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>1.87528402685378e-10</v>
+        <v>1.875284026853786e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>1.425574046812366e-10</v>
+        <v>1.425574046812367e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.555174468388643e-10</v>
+        <v>1.555174468388585e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5234062734703e-10</v>
+        <v>1.523406273470319e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.169226469557512e-10</v>
+        <v>1.169226469557448e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.897176400077593e-10</v>
+        <v>1.89717640007761e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.897176400077593e-10</v>
+        <v>1.89717640007761e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>1.897176400077593e-10</v>
+        <v>1.89717640007761e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.600204262131995e-10</v>
+        <v>1.600204262131978e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>1.677436575358712e-10</v>
+        <v>1.677436575358765e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.897295965804039e-10</v>
+        <v>1.897295965804055e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>1.22498642358315e-10</v>
+        <v>1.224986423583171e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.502037831907652e-10</v>
+        <v>2.50203783190761e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.277487448564602e-10</v>
+        <v>1.277487448564598e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.897176400077593e-10</v>
+        <v>1.89717640007761e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.535291452494803e-10</v>
+        <v>2.535291452494805e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.398306365670833e-10</v>
+        <v>2.398306365670881e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>2.046313922917762e-10</v>
+        <v>2.046313922917751e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.285458658293875e-10</v>
+        <v>2.285458658293908e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>2.031290461002994e-10</v>
+        <v>2.031290461003009e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.057195407047926e-10</v>
+        <v>2.057195407047918e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>2.510724527464471e-10</v>
+        <v>2.510724527464519e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>2.062918554416732e-10</v>
+        <v>2.062918554416773e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>2.179954968183852e-10</v>
+        <v>2.179954968183864e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>2.383793921988718e-10</v>
+        <v>2.383793921988729e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>2.494691727876043e-10</v>
+        <v>2.494691727876098e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>2.685085728051408e-10</v>
+        <v>2.68508572805159e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>2.812573258106498e-10</v>
+        <v>2.812573258106514e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>2.151517816600266e-10</v>
+        <v>2.151517816600334e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>2.17746838411909e-10</v>
+        <v>2.177468384119118e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>2.360088174049503e-10</v>
+        <v>2.360088174049578e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.091708394318908e-10</v>
+        <v>2.091708394318971e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.079966017404695e-10</v>
+        <v>2.079966017404725e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>2.36519755429071e-10</v>
+        <v>2.365197554290748e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>2.110603752988919e-10</v>
+        <v>2.110603752988945e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>2.725439834026055e-10</v>
+        <v>2.725439834026083e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>2.165072994081611e-10</v>
+        <v>2.165072994081686e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>2.438483694316773e-10</v>
+        <v>2.438483694316825e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>2.322082608832509e-10</v>
+        <v>2.322082608832651e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.310354437185991e-10</v>
+        <v>2.310354437186021e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.250584741570272e-10</v>
+        <v>2.250584741570261e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.115925785412932e-10</v>
+        <v>2.115925785412997e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.273340947170905e-10</v>
+        <v>3.273340947170946e-10</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.182167612535215e-10</v>
+        <v>2.182167612535218e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>2.416096154677831e-10</v>
+        <v>2.416096154677714e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.403917834386558e-10</v>
+        <v>2.403917834386526e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.236824536468969e-10</v>
+        <v>2.236824536468959e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.200089763578499e-10</v>
+        <v>2.200089763578474e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.449899187458018e-10</v>
+        <v>2.449899187458029e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>2.403917834386558e-10</v>
+        <v>2.403917834386526e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.403917834386558e-10</v>
+        <v>2.403917834386526e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>2.394494724153354e-10</v>
+        <v>2.394494724153358e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>2.403917834386558e-10</v>
+        <v>2.403917834386526e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>2.403917834386558e-10</v>
+        <v>2.403917834386526e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.382025461162759e-10</v>
+        <v>2.382025461162719e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>2.232024314455798e-10</v>
+        <v>2.232024314455812e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.279262146275376e-10</v>
+        <v>2.279262146275371e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>2.267683012268624e-10</v>
+        <v>2.267683012268632e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.138588632731638e-10</v>
+        <v>2.138588632731673e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>2.403917834386558e-10</v>
+        <v>2.403917834386526e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>2.403917834386558e-10</v>
+        <v>2.403917834386526e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.403917834386558e-10</v>
+        <v>2.403917834386526e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>2.29567497732828e-10</v>
+        <v>2.29567497732824e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.376388204684669e-10</v>
+        <v>2.376388204684641e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>2.403961414689819e-10</v>
+        <v>2.403961414689855e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>2.158912481207557e-10</v>
+        <v>2.158912481207592e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.624382723647078e-10</v>
+        <v>2.624382723647051e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.178048488315138e-10</v>
+        <v>2.178048488315093e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.403917834386558e-10</v>
+        <v>2.403917834386526e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.638157569581662e-10</v>
+        <v>2.638157569581668e-10</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.325984906789595e-11</v>
+        <v>9.325984906791577e-11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.806060479258897e-11</v>
+        <v>5.806060479258921e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>8.197507833020029e-11</v>
+        <v>8.197507833020293e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>5.655825860111245e-11</v>
+        <v>5.655825860111762e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>5.914875320560565e-11</v>
+        <v>5.914875320560692e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>1.008839577361452e-10</v>
+        <v>1.008839577361503e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.972106794248594e-11</v>
+        <v>5.972106794248921e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>7.142470931919815e-11</v>
+        <v>7.142470931920169e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>8.701606539231985e-11</v>
+        <v>8.701606539231915e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>1.028983852884171e-10</v>
+        <v>1.028983852884203e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.219377853059535e-10</v>
+        <v>1.219377853059476e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.346865383114625e-10</v>
+        <v>1.346865383114628e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>6.858099416083937e-11</v>
+        <v>6.858099416084239e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>6.755834340160665e-11</v>
+        <v>6.755834340160961e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>8.58203223946484e-11</v>
+        <v>8.582032239465675e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.260005193270376e-11</v>
+        <v>6.260005193270809e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>6.142581424128219e-11</v>
+        <v>6.142581424128669e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>8.994896792988366e-11</v>
+        <v>8.994896792988839e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>6.448958779970488e-11</v>
+        <v>6.448958779970802e-11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.223554883923035e-10</v>
+        <v>1.22355488392309e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.783274690371893e-11</v>
+        <v>5.783274690371481e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>9.365987442137523e-11</v>
+        <v>9.365987442138114e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>8.201976587294875e-11</v>
+        <v>8.201976587295688e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.446465621941187e-11</v>
+        <v>8.446465621941417e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.848768665783968e-11</v>
+        <v>7.84876866578521e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.502179104210628e-11</v>
+        <v>6.502179104211239e-11</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.807633072179037e-10</v>
+        <v>1.807633072179068e-10</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.164597375433414e-11</v>
+        <v>7.164597375433433e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>9.503882796859563e-11</v>
+        <v>9.503882796857804e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>9.382099593946861e-11</v>
+        <v>9.382099593947579e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>7.711166614770994e-11</v>
+        <v>7.711166614771039e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>7.343818885866275e-11</v>
+        <v>7.343818885866302e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>9.480142373549985e-11</v>
+        <v>9.480142373550426e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>9.382099593946861e-11</v>
+        <v>9.382099593947584e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>9.382099593946861e-11</v>
+        <v>9.382099593947584e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>8.808614560878339e-11</v>
+        <v>8.808614560878293e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>9.382099593946861e-11</v>
+        <v>9.382099593947579e-11</v>
       </c>
       <c r="L7" t="n">
-        <v>9.382099593946861e-11</v>
+        <v>9.382099593947584e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>9.163175861708871e-11</v>
+        <v>9.163175861708937e-11</v>
       </c>
       <c r="N7" t="n">
-        <v>7.663164394639279e-11</v>
+        <v>7.663164394639328e-11</v>
       </c>
       <c r="O7" t="n">
-        <v>7.773771961723561e-11</v>
+        <v>7.773771961723158e-11</v>
       </c>
       <c r="P7" t="n">
-        <v>7.657980621656037e-11</v>
+        <v>7.65798062165627e-11</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.728807577397695e-11</v>
+        <v>6.728807577397459e-11</v>
       </c>
       <c r="R7" t="n">
-        <v>9.382099593946861e-11</v>
+        <v>9.382099593947584e-11</v>
       </c>
       <c r="S7" t="n">
-        <v>9.382099593946861e-11</v>
+        <v>9.382099593947579e-11</v>
       </c>
       <c r="T7" t="n">
-        <v>9.382099593946861e-11</v>
+        <v>9.382099593947584e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>7.937900272252605e-11</v>
+        <v>7.937900272252497e-11</v>
       </c>
       <c r="V7" t="n">
-        <v>7.896426796402462e-11</v>
+        <v>7.896426796402983e-11</v>
       </c>
       <c r="W7" t="n">
-        <v>9.020764645867965e-11</v>
+        <v>9.020764645868482e-11</v>
       </c>
       <c r="X7" t="n">
-        <v>6.570275311045389e-11</v>
+        <v>6.570275311045833e-11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.158674848655209e-10</v>
+        <v>1.158674848655191e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.123406133232672e-11</v>
+        <v>7.123406133233047e-11</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.382099593946861e-11</v>
+        <v>9.382099593947579e-11</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.172449694589793e-10</v>
+        <v>1.172449694589795e-10</v>
       </c>
     </row>
   </sheetData>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.679465060163736e-10</v>
+        <v>1.679465060163783e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>8.720089850731081e-11</v>
+        <v>8.720089850731107e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.810874684619652e-10</v>
+        <v>1.810874684619662e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>1.030484405412814e-10</v>
+        <v>1.030484405412816e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>1.065929076650376e-10</v>
+        <v>1.06592907665038e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>2.095646829869146e-10</v>
+        <v>2.095646829869175e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>8.762740020482293e-11</v>
+        <v>8.762740020482242e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>1.418657281550868e-10</v>
+        <v>1.418657281550853e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>1.790936406625931e-10</v>
+        <v>1.790936406625958e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.332710573227532e-10</v>
+        <v>1.332710573227549e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>2.462079324518384e-10</v>
+        <v>2.462079324518345e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>2.821190992966312e-10</v>
+        <v>2.82119099296632e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>9.187877270949554e-11</v>
+        <v>9.187877270949348e-11</v>
       </c>
       <c r="O2" t="n">
-        <v>1.121808340470299e-10</v>
+        <v>1.121808340470269e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>1.737552600687139e-10</v>
+        <v>1.73755260068718e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.183396674918961e-10</v>
+        <v>1.18339667491897e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>8.838716867316244e-11</v>
+        <v>8.838716867316412e-11</v>
       </c>
       <c r="S2" t="n">
-        <v>1.756433028193861e-10</v>
+        <v>1.756433028193875e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>9.841201673138959e-11</v>
+        <v>9.841201673138773e-11</v>
       </c>
       <c r="U2" t="n">
-        <v>2.342364903177326e-10</v>
+        <v>2.342364903177318e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>1.212737150842134e-10</v>
+        <v>1.212737150842214e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>2.016633784650455e-10</v>
+        <v>2.016633784650477e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>2.006437123319255e-10</v>
+        <v>2.006437123319268e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.277404877637324e-10</v>
+        <v>2.277404877637347e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.492725959377559e-10</v>
+        <v>1.492725959377539e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.092963224183576e-10</v>
+        <v>1.092963224183554e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.036380961948804e-10</v>
+        <v>4.036380961948808e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.267367395922662e-10</v>
+        <v>1.267367395922693e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>1.874306162262639e-10</v>
+        <v>1.874306162262642e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>1.862497809154074e-10</v>
+        <v>1.862497809154032e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.497656789322916e-10</v>
+        <v>1.497656789322925e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.343931901017068e-10</v>
+        <v>1.343931901017069e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>1.985901977257338e-10</v>
+        <v>1.985901977257398e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.862497809154074e-10</v>
+        <v>1.862497809154032e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.862497809154074e-10</v>
+        <v>1.862497809154032e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.840586216544195e-10</v>
+        <v>1.840586216544242e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.862497809154074e-10</v>
+        <v>1.862497809154032e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.862497809154074e-10</v>
+        <v>1.862497809154032e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>1.840343786171356e-10</v>
+        <v>1.84034378617136e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>1.401172175770832e-10</v>
+        <v>1.40117217577098e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.527948465488877e-10</v>
+        <v>1.527948465488985e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.496872533529986e-10</v>
+        <v>1.49687253353001e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.150410686513907e-10</v>
+        <v>1.150410686513917e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.862497809154074e-10</v>
+        <v>1.862497809154032e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.862497809154074e-10</v>
+        <v>1.862497809154032e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>1.862497809154074e-10</v>
+        <v>1.862497809154032e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.572053676104638e-10</v>
+        <v>1.572053676104681e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>1.647685018612556e-10</v>
+        <v>1.647685018612616e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86261476941082e-10</v>
+        <v>1.862614769410863e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>1.204955571476332e-10</v>
+        <v>1.204955571476487e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.454275599253253e-10</v>
+        <v>2.454275599253257e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.256312542950371e-10</v>
+        <v>1.256312542950312e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.862497809154074e-10</v>
+        <v>1.862497809154032e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.485784387915839e-10</v>
+        <v>2.485784387915842e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.31285762409946e-10</v>
+        <v>2.312857624099514e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>2.026053713418052e-10</v>
+        <v>2.02605371341806e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.360754889123927e-10</v>
+        <v>2.36075488912374e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>2.045837972204758e-10</v>
+        <v>2.045837972204671e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.078967538300566e-10</v>
+        <v>2.07896753830076e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>2.464550992104029e-10</v>
+        <v>2.464550992103776e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>2.020103914961953e-10</v>
+        <v>2.020103914961834e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>2.217796251354633e-10</v>
+        <v>2.217796251354713e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>2.353273072041657e-10</v>
+        <v>2.353273072041642e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>2.18646968540797e-10</v>
+        <v>2.186469685407801e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>2.598111333536059e-10</v>
+        <v>2.598111333536179e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>2.714924178032051e-10</v>
+        <v>2.714924178031768e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>2.035599668520122e-10</v>
+        <v>2.035599668519946e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>2.109598298107037e-10</v>
+        <v>2.1095982981065e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>2.334029850521909e-10</v>
+        <v>2.334029850521941e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.132046522806824e-10</v>
+        <v>2.132046522806603e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.022873181812528e-10</v>
+        <v>2.022873181812534e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>2.340911544642941e-10</v>
+        <v>2.340911544642818e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>2.059412575807676e-10</v>
+        <v>2.059412575807817e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>2.554476832714965e-10</v>
+        <v>2.554476832714552e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>2.20104744446909e-10</v>
+        <v>2.201047444469359e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>2.435751664939851e-10</v>
+        <v>2.435751664939967e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>2.432035101619836e-10</v>
+        <v>2.432035101620249e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.530799666204774e-10</v>
+        <v>2.530799666204588e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.244793414664128e-10</v>
+        <v>2.244793414664203e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.099084591936971e-10</v>
+        <v>2.099084591936772e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.17295729188174e-10</v>
+        <v>3.172957291881952e-10</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.162652864578693e-10</v>
+        <v>2.162652864578889e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>2.391379264935967e-10</v>
+        <v>2.391379264935569e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.379570911827389e-10</v>
+        <v>2.379570911827008e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.216116820324903e-10</v>
+        <v>2.216116820324771e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.180296303308248e-10</v>
+        <v>2.180296303308427e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.424550282016118e-10</v>
+        <v>2.42455028201585e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>2.379570911827389e-10</v>
+        <v>2.379570911827008e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.379570911827389e-10</v>
+        <v>2.379570911827008e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>2.371369844739387e-10</v>
+        <v>2.371369844738907e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>2.379570911827389e-10</v>
+        <v>2.379570911827008e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>2.379570911827389e-10</v>
+        <v>2.379570911827008e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.357416888844698e-10</v>
+        <v>2.357416888844936e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>2.211423135618284e-10</v>
+        <v>2.211423135618531e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.257631604538206e-10</v>
+        <v>2.257631604538225e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>2.246304792251153e-10</v>
+        <v>2.246304792251275e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.120023517374209e-10</v>
+        <v>2.120023517374542e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>2.379570911827389e-10</v>
+        <v>2.379570911827008e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>2.379570911827389e-10</v>
+        <v>2.379570911827008e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.379570911827389e-10</v>
+        <v>2.379570911827008e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>2.273707435898073e-10</v>
+        <v>2.273707435898082e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.359580834855683e-10</v>
+        <v>2.359580834855593e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>2.379613542467547e-10</v>
+        <v>2.379613542467376e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>2.139904487444659e-10</v>
+        <v>2.13990448744469e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.595266967312874e-10</v>
+        <v>2.59526696731264e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.158623500482929e-10</v>
+        <v>2.15862350048286e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.379570911827389e-10</v>
+        <v>2.379570911827008e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.607783048671e-10</v>
+        <v>2.607783048671036e-10</v>
       </c>
     </row>
     <row r="6">
@@ -2990,82 +2990,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.582963423479892e-11</v>
+        <v>8.582963423479714e-11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.714924316665784e-11</v>
+        <v>5.71492431666583e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>9.061936073724564e-11</v>
+        <v>9.061936073724851e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>5.912766904532937e-11</v>
+        <v>5.912766904532944e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>6.244062565491008e-11</v>
+        <v>6.244062565491089e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>9.740196156314759e-11</v>
+        <v>9.740196156314675e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>5.655426332104695e-11</v>
+        <v>5.655426332104809e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>7.632349696031559e-11</v>
+        <v>7.632349696031464e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>8.502429967563929e-11</v>
+        <v>8.502429967564551e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>7.319084036565054e-11</v>
+        <v>7.319084036565191e-11</v>
       </c>
       <c r="L6" t="n">
-        <v>1.143550051784588e-10</v>
+        <v>1.143550051784597e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.260362896280582e-10</v>
+        <v>1.260362896280587e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.810383867686382e-11</v>
+        <v>5.810383867686433e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>6.190669216344857e-11</v>
+        <v>6.190669216344686e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>8.434984740493781e-11</v>
+        <v>8.434984740493636e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.77485241055352e-11</v>
+        <v>6.774852410553421e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>5.683119000610793e-11</v>
+        <v>5.683119000610705e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>8.863502628914582e-11</v>
+        <v>8.863502628914078e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>6.048512940561879e-11</v>
+        <v>6.048512940561825e-11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.063945456242415e-10</v>
+        <v>1.063945456242395e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>6.206889664699503e-11</v>
+        <v>6.206889664700205e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>9.452202884672809e-11</v>
+        <v>9.45220288467253e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>9.415037251472995e-11</v>
+        <v>9.415037251472701e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.076238384453282e-10</v>
+        <v>1.076238384453247e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.902321329126582e-11</v>
+        <v>7.902321329126325e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.445233101854917e-11</v>
+        <v>6.445233101854871e-11</v>
       </c>
       <c r="AB6" t="n">
         <v>1.71839601013028e-10</v>
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.080915828272207e-11</v>
+        <v>7.080915828272254e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>9.368179831844874e-11</v>
+        <v>9.368179831844865e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>9.250096300759009e-11</v>
+        <v>9.25009630075942e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>7.61555538573427e-11</v>
+        <v>7.615555385734286e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>7.2573502155678e-11</v>
+        <v>7.257350215567788e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>9.340189055435634e-11</v>
+        <v>9.340189055435688e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>9.250096300759009e-11</v>
+        <v>9.25009630075942e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>9.250096300759009e-11</v>
+        <v>9.25009630075942e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>8.683397694541258e-11</v>
+        <v>8.683397694541376e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>9.250096300759009e-11</v>
+        <v>9.25009630075942e-11</v>
       </c>
       <c r="L7" t="n">
-        <v>9.250096300759009e-11</v>
+        <v>9.25009630075942e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>9.028556070932271e-11</v>
+        <v>9.028556070932296e-11</v>
       </c>
       <c r="N7" t="n">
-        <v>7.568618538668182e-11</v>
+        <v>7.568618538668702e-11</v>
       </c>
       <c r="O7" t="n">
-        <v>7.671002280656502e-11</v>
+        <v>7.671002280657478e-11</v>
       </c>
       <c r="P7" t="n">
-        <v>7.557734157786103e-11</v>
+        <v>7.557734157786518e-11</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.654622356227392e-11</v>
+        <v>6.654622356228276e-11</v>
       </c>
       <c r="R7" t="n">
-        <v>9.250096300759009e-11</v>
+        <v>9.25009630075942e-11</v>
       </c>
       <c r="S7" t="n">
-        <v>9.250096300759009e-11</v>
+        <v>9.25009630075942e-11</v>
       </c>
       <c r="T7" t="n">
-        <v>9.250096300759009e-11</v>
+        <v>9.25009630075942e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>7.831760594255334e-11</v>
+        <v>7.831760594255233e-11</v>
       </c>
       <c r="V7" t="n">
-        <v>7.792223568565345e-11</v>
+        <v>7.792223568565487e-11</v>
       </c>
       <c r="W7" t="n">
-        <v>8.890821659950061e-11</v>
+        <v>8.890821659951075e-11</v>
       </c>
       <c r="X7" t="n">
-        <v>6.493731109721093e-11</v>
+        <v>6.493731109721111e-11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.140705685561406e-10</v>
+        <v>1.140705685561401e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.040622187314598e-11</v>
+        <v>7.040622187315348e-11</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.250096300759009e-11</v>
+        <v>9.25009630075942e-11</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.153221766919523e-10</v>
+        <v>1.153221766919527e-10</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.547037637550888e-10</v>
+        <v>1.547037637550834e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>8.162363145617508e-11</v>
+        <v>8.162363145617512e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.595374187040568e-10</v>
+        <v>1.595374187040506e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>9.134454942527462e-11</v>
+        <v>9.13445494252747e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.150688376160732e-10</v>
+        <v>1.150688376160728e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>1.960355311263975e-10</v>
+        <v>1.960355311263993e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>9.093647295271561e-11</v>
+        <v>9.093647295270985e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>1.322355979627167e-10</v>
+        <v>1.322355979627111e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>1.724822680637236e-10</v>
+        <v>1.724822680637158e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.303768626960552e-10</v>
+        <v>1.303768626960499e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>2.210523968156857e-10</v>
+        <v>2.210523968156826e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>2.550954443340603e-10</v>
+        <v>2.550954443340609e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>7.848339094653629e-11</v>
+        <v>7.848339094653122e-11</v>
       </c>
       <c r="O2" t="n">
-        <v>1.051727396818313e-10</v>
+        <v>1.05172739681825e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>1.640334835653131e-10</v>
+        <v>1.640334835653127e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.142536986209568e-10</v>
+        <v>1.142536986209516e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>1.063476931309176e-10</v>
+        <v>1.063476931309121e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>1.719344797239061e-10</v>
+        <v>1.719344797239016e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>1.084695563142575e-10</v>
+        <v>1.084695563142523e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>2.421647485421359e-10</v>
+        <v>2.421647485421301e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>1.495968425527601e-10</v>
+        <v>1.495968425527593e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>2.016712548389336e-10</v>
+        <v>2.016712548389277e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>2.176140488274675e-10</v>
+        <v>2.176140488274643e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.115883473485757e-10</v>
+        <v>3.115883473485738e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.476845255673569e-10</v>
+        <v>1.476845255673544e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.132819080383486e-10</v>
+        <v>1.132819080383431e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.813237680538858e-10</v>
+        <v>3.813237680538859e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3410,85 +3410,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.253209211411408e-10</v>
+        <v>1.253209211411392e-10</v>
       </c>
       <c r="C3" t="n">
         <v>1.851603292063749e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>1.839930776516423e-10</v>
+        <v>1.839930776516373e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.48011592830115e-10</v>
+        <v>1.480115928301148e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.329063258327167e-10</v>
+        <v>1.329063258327164e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>1.961591315181809e-10</v>
+        <v>1.961591315181755e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.839930776516423e-10</v>
+        <v>1.839930776516373e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.839930776516423e-10</v>
+        <v>1.839930776516373e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.818543289975625e-10</v>
+        <v>1.818543289975616e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.839930776516423e-10</v>
+        <v>1.839930776516373e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.839930776516423e-10</v>
+        <v>1.839930776516373e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>1.817458090002734e-10</v>
+        <v>1.817458090002746e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>1.38512340719972e-10</v>
+        <v>1.385123407199706e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.510108421353136e-10</v>
+        <v>1.510108421353068e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.479471574318636e-10</v>
+        <v>1.479471574318572e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.137905032583169e-10</v>
+        <v>1.137905032583148e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.839930776516423e-10</v>
+        <v>1.839930776516373e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.839930776516423e-10</v>
+        <v>1.839930776516373e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>1.839930776516423e-10</v>
+        <v>1.839930776516373e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.553675456302326e-10</v>
+        <v>1.553675456302271e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>1.628862283985602e-10</v>
+        <v>1.628862283985579e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.840046084189579e-10</v>
+        <v>1.840046084189536e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>1.191679229903718e-10</v>
+        <v>1.191679229903705e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.423492508653211e-10</v>
+        <v>2.423492508653175e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.242310557110556e-10</v>
+        <v>1.242310557110503e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.839930776516423e-10</v>
+        <v>1.839930776516373e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.453785124208377e-10</v>
+        <v>2.453785124208373e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.251781196643572e-10</v>
+        <v>2.251781196643538e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.992830716612373e-10</v>
+        <v>1.992830716612368e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.269399301336144e-10</v>
+        <v>2.269399301336099e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.990719186870802e-10</v>
+        <v>1.990719186870799e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.09743413675766e-10</v>
+        <v>2.097434136757649e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>2.402430635290822e-10</v>
+        <v>2.402430635290813e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>2.019356909602255e-10</v>
+        <v>2.01935690960222e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>2.169887370675604e-10</v>
+        <v>2.169887370675575e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>2.320274422567456e-10</v>
+        <v>2.320274422567422e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>2.163112498892345e-10</v>
+        <v>2.163112498892305e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>2.493614173099589e-10</v>
+        <v>2.493614173099577e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>2.603415427600588e-10</v>
+        <v>2.603415427600594e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.973966888004451e-10</v>
+        <v>1.973966888004416e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>2.071246430123047e-10</v>
+        <v>2.071246430123011e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>2.285786929800825e-10</v>
+        <v>2.285786929800805e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.104345459116119e-10</v>
+        <v>2.104345459116087e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.075528997474961e-10</v>
+        <v>2.075528997474928e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>2.31458513301711e-10</v>
+        <v>2.314585133017057e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>2.083262939616489e-10</v>
+        <v>2.083262939616449e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>2.570566216005008e-10</v>
+        <v>2.570566216004969e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>2.316179175448806e-10</v>
+        <v>2.316179175448964e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>2.422972186442926e-10</v>
+        <v>2.422972186442896e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>2.48108179843375e-10</v>
+        <v>2.481081798433722e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.823607081523926e-10</v>
+        <v>2.823607081523895e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.226196897689877e-10</v>
+        <v>2.22619689768983e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.100803396555921e-10</v>
+        <v>2.100803396555891e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.078403878626709e-10</v>
+        <v>3.078403878626699e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.144684185623333e-10</v>
+        <v>2.144684185623287e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>2.370209822018975e-10</v>
+        <v>2.370209822018968e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.358537306471626e-10</v>
+        <v>2.358537306471592e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.197263905901256e-10</v>
+        <v>2.197263905901247e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.162449686723703e-10</v>
+        <v>2.162449686723698e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.40288114420501e-10</v>
+        <v>2.402881144204953e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>2.358537306471626e-10</v>
+        <v>2.358537306471592e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.358537306471626e-10</v>
+        <v>2.358537306471592e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>2.354434484148341e-10</v>
+        <v>2.354434484148325e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>2.358537306471626e-10</v>
+        <v>2.358537306471592e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>2.358537306471626e-10</v>
+        <v>2.358537306471592e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.336064619957981e-10</v>
+        <v>2.336064619957977e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>2.192765360973483e-10</v>
+        <v>2.192765360973434e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.238320930984241e-10</v>
+        <v>2.238320930984202e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>2.227154159996179e-10</v>
+        <v>2.227154159996148e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.102657166410484e-10</v>
+        <v>2.10265716641042e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>2.358537306471626e-10</v>
+        <v>2.358537306471592e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>2.358537306471626e-10</v>
+        <v>2.358537306471592e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.358537306471626e-10</v>
+        <v>2.358537306471592e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>2.254200603633288e-10</v>
+        <v>2.254200603633231e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.364617426338251e-10</v>
+        <v>2.364617426338434e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>2.358579334764501e-10</v>
+        <v>2.358579334764451e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>2.122257229885285e-10</v>
+        <v>2.122257229885256e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.571238705307656e-10</v>
+        <v>2.571238705307632e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.140711754109118e-10</v>
+        <v>2.140711754109076e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.358537306471626e-10</v>
+        <v>2.358537306471592e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.582899385342123e-10</v>
+        <v>2.582899385342112e-10</v>
       </c>
     </row>
     <row r="6">
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.093280433677096e-11</v>
+        <v>8.093280433676635e-11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.503775633364943e-11</v>
+        <v>5.503775633364947e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>8.26946148060276e-11</v>
+        <v>8.26946148060233e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>5.482660335949226e-11</v>
+        <v>5.482660335949196e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>6.549809834817789e-11</v>
+        <v>6.549809834817745e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>9.241202332612005e-11</v>
+        <v>9.2412023326111e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>5.769037563263955e-11</v>
+        <v>5.769037563263505e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>7.274342173997448e-11</v>
+        <v>7.274342173996996e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>8.258873480906717e-11</v>
+        <v>8.258873480906411e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>7.206593456164746e-11</v>
+        <v>7.206593456164339e-11</v>
       </c>
       <c r="L6" t="n">
-        <v>1.051161019823738e-10</v>
+        <v>1.051161019823699e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.160962274324709e-10</v>
+        <v>1.160962274324702e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.31513734728588e-11</v>
+        <v>5.315137347285453e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>5.929360280933532e-11</v>
+        <v>5.929360280933011e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>8.074765277711372e-11</v>
+        <v>8.074765277710917e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.61892305840255e-11</v>
+        <v>6.618923058402097e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>6.330758441991022e-11</v>
+        <v>6.33075844199058e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>8.721319797412491e-11</v>
+        <v>8.721319797411864e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>6.408097863406267e-11</v>
+        <v>6.408097863405774e-11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.092255813975318e-10</v>
+        <v>1.09225581397526e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>7.241906740340653e-11</v>
+        <v>7.241906740340575e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>9.446617844132428e-11</v>
+        <v>9.446617844131835e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.002771396404032e-10</v>
+        <v>1.00277139640401e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.381153928248056e-10</v>
+        <v>1.381153928248025e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.83743744414007e-11</v>
+        <v>7.837437444139529e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.583502432800618e-11</v>
+        <v>6.58350243280018e-11</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.635950725350822e-10</v>
+        <v>1.635950725350829e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.02231032347435e-11</v>
+        <v>7.022310323474125e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>9.277566687430977e-11</v>
+        <v>9.277566687430924e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>9.160841531957808e-11</v>
+        <v>9.16084153195719e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>7.548107526253768e-11</v>
+        <v>7.548107526253739e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>7.199965334478278e-11</v>
+        <v>7.199965334478274e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>9.245707421752746e-11</v>
+        <v>9.245707421752444e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>9.160841531957808e-11</v>
+        <v>9.16084153195719e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>9.160841531957808e-11</v>
+        <v>9.16084153195719e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>8.600474096715404e-11</v>
+        <v>8.600474096715307e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>9.160841531957808e-11</v>
+        <v>9.16084153195719e-11</v>
       </c>
       <c r="L7" t="n">
-        <v>9.160841531957808e-11</v>
+        <v>9.16084153195719e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>8.936114666820965e-11</v>
+        <v>8.936114666820903e-11</v>
       </c>
       <c r="N7" t="n">
-        <v>7.503122076975823e-11</v>
+        <v>7.50312207697566e-11</v>
       </c>
       <c r="O7" t="n">
-        <v>7.600105289545378e-11</v>
+        <v>7.600105289544921e-11</v>
       </c>
       <c r="P7" t="n">
-        <v>7.488437579664822e-11</v>
+        <v>7.488437579664377e-11</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.602040131345836e-11</v>
+        <v>6.602040131345483e-11</v>
       </c>
       <c r="R7" t="n">
-        <v>9.160841531957808e-11</v>
+        <v>9.16084153195719e-11</v>
       </c>
       <c r="S7" t="n">
-        <v>9.160841531957808e-11</v>
+        <v>9.16084153195719e-11</v>
       </c>
       <c r="T7" t="n">
-        <v>9.160841531957808e-11</v>
+        <v>9.16084153195719e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>7.758902016036018e-11</v>
+        <v>7.758902016035238e-11</v>
       </c>
       <c r="V7" t="n">
-        <v>7.726289249235133e-11</v>
+        <v>7.726289249235199e-11</v>
       </c>
       <c r="W7" t="n">
-        <v>8.802689327347729e-11</v>
+        <v>8.802689327347391e-11</v>
       </c>
       <c r="X7" t="n">
-        <v>6.439468278555931e-11</v>
+        <v>6.43946827855551e-11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.128785552031811e-10</v>
+        <v>1.12878555203176e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.982586008332537e-11</v>
+        <v>6.982586008332009e-11</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.160841531957808e-11</v>
+        <v>9.16084153195719e-11</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.140446232066242e-10</v>
+        <v>1.140446232066238e-10</v>
       </c>
     </row>
   </sheetData>
@@ -4006,85 +4006,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.014752085058045e-10</v>
+        <v>1.01475208505805e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>7.391417982258968e-11</v>
+        <v>7.391417982258937e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.482943141026156e-10</v>
+        <v>1.482943141026162e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>7.528684725858096e-11</v>
+        <v>7.528684725858077e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>9.234492856691453e-11</v>
+        <v>9.234492856691427e-11</v>
       </c>
       <c r="G2" t="n">
-        <v>1.185062243867395e-10</v>
+        <v>1.185062243867417e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>1.143745974755519e-10</v>
+        <v>1.143745974755526e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>1.048096560674329e-10</v>
+        <v>1.048096560674332e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>1.163633580532868e-10</v>
+        <v>1.16363358053287e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.625455496887726e-10</v>
+        <v>1.625455496887733e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>1.505853681443939e-10</v>
+        <v>1.505853681443941e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>1.647172398548597e-10</v>
+        <v>1.647172398548609e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>1.327561480883053e-10</v>
+        <v>1.327561480883057e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>8.658630407440228e-11</v>
+        <v>8.658630407440246e-11</v>
       </c>
       <c r="P2" t="n">
-        <v>1.08767598536296e-10</v>
+        <v>1.087675985362974e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.097442546118186e-10</v>
+        <v>1.097442546118194e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>1.016035669047513e-10</v>
+        <v>1.016035669047519e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>1.165371258971879e-10</v>
+        <v>1.165371258971897e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>9.569771487187479e-11</v>
+        <v>9.569771487187551e-11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.507225641650878e-10</v>
+        <v>1.507225641650894e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>8.822510042759445e-11</v>
+        <v>8.822510042759244e-11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.578831273562347e-10</v>
+        <v>1.578831273562348e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>1.136080549523728e-10</v>
+        <v>1.136080549523744e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.792827501892355e-11</v>
+        <v>9.792827501892402e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.127469310763946e-10</v>
+        <v>1.127469310763954e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.519340148424597e-11</v>
+        <v>9.519340148424642e-11</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.752831837292077e-10</v>
+        <v>1.752831837292076e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.178965854705586e-10</v>
+        <v>1.178965854705598e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>1.746718899217412e-10</v>
+        <v>1.74671889921741e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>1.734181763288323e-10</v>
+        <v>1.73418176328832e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.393440380900122e-10</v>
+        <v>1.393440380900121e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.250956484763775e-10</v>
+        <v>1.250956484763772e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>1.84930939883347e-10</v>
+        <v>1.849309398833477e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.734181763288323e-10</v>
+        <v>1.73418176328832e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.734181763288323e-10</v>
+        <v>1.73418176328832e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.713438023106032e-10</v>
+        <v>1.713438023106037e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.734181763288323e-10</v>
+        <v>1.73418176328832e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.734181763288323e-10</v>
+        <v>1.73418176328832e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>1.711142600401937e-10</v>
+        <v>1.711142600401933e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>1.303796548557502e-10</v>
+        <v>1.303796548557499e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.422070142575652e-10</v>
+        <v>1.422070142575653e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.393078426787017e-10</v>
+        <v>1.393078426787019e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.069853256465926e-10</v>
+        <v>1.06985325646592e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.734181763288323e-10</v>
+        <v>1.73418176328832e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.734181763288323e-10</v>
+        <v>1.73418176328832e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>1.734181763288323e-10</v>
+        <v>1.73418176328832e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.463269283300068e-10</v>
+        <v>1.463269283300061e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>1.533373166638092e-10</v>
+        <v>1.533373166638071e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.734290879195369e-10</v>
+        <v>1.73429087919537e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>1.120739897762436e-10</v>
+        <v>1.120739897762439e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.286358861814093e-10</v>
+        <v>2.286358861814085e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.168652434149765e-10</v>
+        <v>1.168652434149762e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.734181763288323e-10</v>
+        <v>1.73418176328832e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.309517969780574e-10</v>
+        <v>2.30951796978057e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4182,85 +4182,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.974652251985401e-10</v>
+        <v>1.974652251985408e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.882163035915888e-10</v>
+        <v>1.882163035915898e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.145302394108837e-10</v>
+        <v>2.145302394108833e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.850533809683878e-10</v>
+        <v>1.85053380968388e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.932155025725437e-10</v>
+        <v>1.932155025725443e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>2.03672830498855e-10</v>
+        <v>2.036728304988556e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0216690100574e-10</v>
+        <v>2.021669010057419e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.986805921796929e-10</v>
+        <v>1.986805921796955e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>2.030517265605084e-10</v>
+        <v>2.030517265605109e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>2.197246474355792e-10</v>
+        <v>2.197246474355801e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>2.153653017061956e-10</v>
+        <v>2.153653017061961e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>2.190520371444674e-10</v>
+        <v>2.19052037144468e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>2.088667603570238e-10</v>
+        <v>2.088667603570244e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>1.920383943676366e-10</v>
+        <v>1.92038394367637e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>2.00123215733088e-10</v>
+        <v>2.001232157330879e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.004791954041401e-10</v>
+        <v>2.00479195404141e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>1.975120103276953e-10</v>
+        <v>1.975120103276962e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>2.029551172217349e-10</v>
+        <v>2.029551172217365e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>1.953593966117281e-10</v>
+        <v>1.953593966117285e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>2.154153080447025e-10</v>
+        <v>2.154153080447031e-10</v>
       </c>
       <c r="V4" t="n">
         <v>1.9937466340752e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>2.180252492442979e-10</v>
+        <v>2.180252492442965e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>2.018875052572375e-10</v>
+        <v>2.018875052572391e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.961724095927673e-10</v>
+        <v>1.961724095927683e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.015736357162713e-10</v>
+        <v>2.015736357162719e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.951755803038841e-10</v>
+        <v>1.951755803038849e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.24072917851047e-10</v>
+        <v>2.240729178510469e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.034506242726498e-10</v>
+        <v>2.034506242726509e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>2.249413057659628e-10</v>
+        <v>2.249413057659633e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.236875921730538e-10</v>
+        <v>2.236875921730531e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.084014748289332e-10</v>
+        <v>2.084014748289338e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.051527554011736e-10</v>
+        <v>2.051527554011738e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.278838592989792e-10</v>
+        <v>2.278838592989803e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>2.236875921730538e-10</v>
+        <v>2.236875921730531e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.236875921730538e-10</v>
+        <v>2.236875921730531e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>2.230914528793285e-10</v>
+        <v>2.230914528793292e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>2.236875921730538e-10</v>
+        <v>2.236875921730531e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>2.236875921730538e-10</v>
+        <v>2.236875921730531e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.213836758844179e-10</v>
+        <v>2.213836758844183e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>2.080005564799498e-10</v>
+        <v>2.080005564799497e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.123114900980446e-10</v>
+        <v>2.123114900980465e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>2.112547761013408e-10</v>
+        <v>2.112547761013415e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.994735981932948e-10</v>
+        <v>1.994735981932953e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>2.236875921730538e-10</v>
+        <v>2.236875921730531e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>2.236875921730538e-10</v>
+        <v>2.236875921730531e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.236875921730538e-10</v>
+        <v>2.236875921730531e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>2.138131503989765e-10</v>
+        <v>2.138131503989767e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.231073016393748e-10</v>
+        <v>2.231073016393758e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>2.236915693197343e-10</v>
+        <v>2.236915693197351e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>2.013283565144424e-10</v>
+        <v>2.013283565144421e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.438137990152326e-10</v>
+        <v>2.43813799015233e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.030747122040183e-10</v>
+        <v>2.030747122040202e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.236875921730538e-10</v>
+        <v>2.236875921730531e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.443634736863915e-10</v>
+        <v>2.443634736863923e-10</v>
       </c>
     </row>
     <row r="6">
@@ -4358,85 +4358,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.991230686691788e-11</v>
+        <v>5.991230686691778e-11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.066338525996723e-11</v>
+        <v>5.066338525996716e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>7.697732107926152e-11</v>
+        <v>7.697732107926067e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>4.750046263676599e-11</v>
+        <v>4.750046263676578e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>5.566258424092169e-11</v>
+        <v>5.566258424092162e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>6.258642598486617e-11</v>
+        <v>6.258642598486575e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>6.461398267411805e-11</v>
+        <v>6.461398267411964e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>6.112767384807134e-11</v>
+        <v>6.112767384807299e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>6.06056695608721e-11</v>
+        <v>6.060566956087292e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>8.217172910395755e-11</v>
+        <v>8.21717291039579e-11</v>
       </c>
       <c r="L6" t="n">
-        <v>7.781238337457393e-11</v>
+        <v>7.78123833745739e-11</v>
       </c>
       <c r="M6" t="n">
-        <v>8.149911881284562e-11</v>
+        <v>8.149911881284549e-11</v>
       </c>
       <c r="N6" t="n">
-        <v>7.13138420254017e-11</v>
+        <v>7.131384202540177e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>5.095198985364675e-11</v>
+        <v>5.095198985364694e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>5.903681121909902e-11</v>
+        <v>5.903681121909825e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.292627707251826e-11</v>
+        <v>6.292627707251848e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>5.995909199607353e-11</v>
+        <v>5.995909199607373e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>6.540219889011336e-11</v>
+        <v>6.54021988901142e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>5.780647828010599e-11</v>
+        <v>5.780647828010607e-11</v>
       </c>
       <c r="U6" t="n">
-        <v>7.432890353071224e-11</v>
+        <v>7.432890353071263e-11</v>
       </c>
       <c r="V6" t="n">
-        <v>4.858639596641587e-11</v>
+        <v>4.858639596641701e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>7.693884473030835e-11</v>
+        <v>7.693884473030683e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>6.080110074324821e-11</v>
+        <v>6.080110074324916e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.861949126114543e-11</v>
+        <v>5.861949126114593e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.402071738464898e-11</v>
+        <v>6.402071738464871e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.762266197226187e-11</v>
+        <v>5.762266197226205e-11</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.651999951942461e-11</v>
+        <v>8.65199995194242e-11</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.589770594102813e-11</v>
+        <v>6.589770594102823e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>8.73883874343408e-11</v>
+        <v>8.73883874343407e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>8.613467384143192e-11</v>
+        <v>8.613467384143068e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>7.084855649731116e-11</v>
+        <v>7.084855649731082e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>6.759983706955121e-11</v>
+        <v>6.759983706955088e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>8.679745478498982e-11</v>
+        <v>8.679745478499042e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>8.613467384143192e-11</v>
+        <v>8.613467384143068e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>8.613467384143192e-11</v>
+        <v>8.613467384143068e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>8.064539587969235e-11</v>
+        <v>8.064539587969219e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>8.613467384143192e-11</v>
+        <v>8.613467384143068e-11</v>
       </c>
       <c r="L7" t="n">
-        <v>8.613467384143192e-11</v>
+        <v>8.613467384143068e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>8.383075755279596e-11</v>
+        <v>8.383075755279581e-11</v>
       </c>
       <c r="N7" t="n">
-        <v>7.044763814832732e-11</v>
+        <v>7.044763814832702e-11</v>
       </c>
       <c r="O7" t="n">
-        <v>7.122508558405531e-11</v>
+        <v>7.122508558405651e-11</v>
       </c>
       <c r="P7" t="n">
-        <v>7.016837158735128e-11</v>
+        <v>7.016837158735191e-11</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.192067986167297e-11</v>
+        <v>6.192067986167319e-11</v>
       </c>
       <c r="R7" t="n">
-        <v>8.613467384143192e-11</v>
+        <v>8.613467384143068e-11</v>
       </c>
       <c r="S7" t="n">
-        <v>8.613467384143192e-11</v>
+        <v>8.613467384143068e-11</v>
       </c>
       <c r="T7" t="n">
-        <v>8.613467384143192e-11</v>
+        <v>8.613467384143068e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>7.27267458849867e-11</v>
+        <v>7.272674588498657e-11</v>
       </c>
       <c r="V7" t="n">
-        <v>7.231903419827094e-11</v>
+        <v>7.231903419827155e-11</v>
       </c>
       <c r="W7" t="n">
-        <v>8.260516480574539e-11</v>
+        <v>8.260516480574496e-11</v>
       </c>
       <c r="X7" t="n">
-        <v>6.02419520004533e-11</v>
+        <v>6.024195200045147e-11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.062608806836106e-10</v>
+        <v>1.06260880683611e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.552179387239642e-11</v>
+        <v>6.552179387239753e-11</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.613467384143192e-11</v>
+        <v>8.613467384143068e-11</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.068105553547697e-10</v>
+        <v>1.0681055535477e-10</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.104946568067431e-10</v>
+        <v>1.104946568067391e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>8.830996901734523e-11</v>
+        <v>8.830996901734606e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.272884560678105e-10</v>
+        <v>1.272884560678069e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>6.733216017311419e-11</v>
+        <v>6.73321601731139e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.102744561151813e-10</v>
+        <v>1.10274456115181e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>9.580482796634559e-11</v>
+        <v>9.580482796633574e-11</v>
       </c>
       <c r="H2" t="n">
-        <v>1.063666158704492e-10</v>
+        <v>1.06366615870445e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>1.162258439635326e-10</v>
+        <v>1.162258439635301e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>1.019543705699668e-10</v>
+        <v>1.019543705699644e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.095450271238743e-10</v>
+        <v>1.095450271238702e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>1.148695140589306e-10</v>
+        <v>1.14869514058926e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>1.060865921272887e-10</v>
+        <v>1.060865921272884e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>9.864261224785804e-11</v>
+        <v>9.864261224785461e-11</v>
       </c>
       <c r="O2" t="n">
-        <v>8.795983942343099e-11</v>
+        <v>8.795983942342697e-11</v>
       </c>
       <c r="P2" t="n">
-        <v>8.110437603088235e-11</v>
+        <v>8.110437603087862e-11</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.39359909455002e-11</v>
+        <v>9.393599094549762e-11</v>
       </c>
       <c r="R2" t="n">
-        <v>1.159067900726487e-10</v>
+        <v>1.159067900726439e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>1.080157473174813e-10</v>
+        <v>1.080157473174779e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>9.434735918913263e-11</v>
+        <v>9.434735918913353e-11</v>
       </c>
       <c r="U2" t="n">
-        <v>9.411171960638666e-11</v>
+        <v>9.411171960638231e-11</v>
       </c>
       <c r="V2" t="n">
-        <v>9.433301785594957e-11</v>
+        <v>9.433301785594291e-11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.609619728110499e-10</v>
+        <v>1.60961972811046e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>1.558296328067229e-10</v>
+        <v>1.558296328067179e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.260638184617987e-10</v>
+        <v>1.260638184617948e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.079586141911865e-10</v>
+        <v>1.079586141911819e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.068483048214984e-10</v>
+        <v>1.068483048214945e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.130021670372747e-10</v>
+        <v>1.130021670372745e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.142160196502355e-10</v>
+        <v>1.142160196502356e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>1.691860430215728e-10</v>
+        <v>1.691860430215679e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>1.679132741506054e-10</v>
+        <v>1.679132741505953e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.349538508012699e-10</v>
+        <v>1.349538508012693e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.212462676820704e-10</v>
+        <v>1.2124626768207e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>1.790477496767897e-10</v>
+        <v>1.79047749676792e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.679132741506054e-10</v>
+        <v>1.679132741505953e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.679132741506054e-10</v>
+        <v>1.679132741505953e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.659089528321229e-10</v>
+        <v>1.659089528321187e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.679132741506054e-10</v>
+        <v>1.679132741505953e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.679132741506054e-10</v>
+        <v>1.679132741505953e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>1.655300205616307e-10</v>
+        <v>1.6553002056163e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>1.262889185595025e-10</v>
+        <v>1.262889185594995e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.377276528975115e-10</v>
+        <v>1.377276528975021e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.349237427123297e-10</v>
+        <v>1.349237427123294e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.036632835592728e-10</v>
+        <v>1.036632835592736e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.679132741506054e-10</v>
+        <v>1.679132741505953e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.679132741506054e-10</v>
+        <v>1.679132741505953e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>1.679132741506054e-10</v>
+        <v>1.679132741505953e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.417145429395043e-10</v>
+        <v>1.417145429395028e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>1.485177216813465e-10</v>
+        <v>1.485177216813421e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.679238272060934e-10</v>
+        <v>1.679238272060878e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>1.085847436361875e-10</v>
+        <v>1.085847436361833e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.213206505429608e-10</v>
+        <v>2.213206505429558e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.13218565579194e-10</v>
+        <v>1.132185655791898e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.679132741506054e-10</v>
+        <v>1.679132741505953e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.233360286919931e-10</v>
+        <v>2.23336028691992e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4866,85 +4866,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.978814479680743e-10</v>
+        <v>1.978814479680718e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.906042493377047e-10</v>
+        <v>1.90604249337698e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.040025905959866e-10</v>
+        <v>2.040025905959843e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.793738056392999e-10</v>
+        <v>1.793738056392996e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.969526796743378e-10</v>
+        <v>1.969526796743377e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.925271778524256e-10</v>
+        <v>1.925271778524248e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.963768255206996e-10</v>
+        <v>1.963768255206968e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>1.999703983877295e-10</v>
+        <v>1.999703983877243e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.950318567300444e-10</v>
+        <v>1.950318567300461e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.975353190997833e-10</v>
+        <v>1.975353190997814e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.994760320643289e-10</v>
+        <v>1.994760320643261e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>1.94760174513155e-10</v>
+        <v>1.947601745131548e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.935615169000968e-10</v>
+        <v>1.935615169000925e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>1.896677716490426e-10</v>
+        <v>1.896677716490404e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>1.871690357433741e-10</v>
+        <v>1.871690357433729e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.918460087033227e-10</v>
+        <v>1.918460087033303e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>1.99854106991019e-10</v>
+        <v>1.998541069910166e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>1.969779145680662e-10</v>
+        <v>1.969779145680615e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>1.91995947597597e-10</v>
+        <v>1.919959475975974e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>1.919100597367061e-10</v>
+        <v>1.919100597367028e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>1.992390008460875e-10</v>
+        <v>1.992390008460915e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>2.162761920344994e-10</v>
+        <v>2.16276192034497e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>2.144055143699032e-10</v>
+        <v>2.144055143698996e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.035562245690155e-10</v>
+        <v>2.035562245690135e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.969570902144196e-10</v>
+        <v>1.969570902144176e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9655239548708e-10</v>
+        <v>1.965523954870779e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.983705550386292e-10</v>
+        <v>1.98370555038629e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.992378410260769e-10</v>
+        <v>1.992378410260648e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>2.200826286174366e-10</v>
+        <v>2.200826286174274e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.188098597464653e-10</v>
+        <v>2.188098597464615e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.04021117819281e-10</v>
+        <v>2.040211178192811e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.009517761529526e-10</v>
+        <v>2.00951776152952e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.228682453281504e-10</v>
+        <v>2.228682453281469e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>2.188098597464653e-10</v>
+        <v>2.188098597464615e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.188098597464653e-10</v>
+        <v>2.188098597464615e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>2.183425509719796e-10</v>
+        <v>2.18342550971982e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>2.188098597464653e-10</v>
+        <v>2.188098597464615e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>2.188098597464653e-10</v>
+        <v>2.188098597464615e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.164266061574949e-10</v>
+        <v>2.164266061574947e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>2.036382709113684e-10</v>
+        <v>2.036382709113689e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.078075552571725e-10</v>
+        <v>2.078075552571758e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>2.067855629198506e-10</v>
+        <v>2.067855629198518e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.953914926374077e-10</v>
+        <v>1.953914926374051e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>2.188098597464653e-10</v>
+        <v>2.188098597464615e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>2.188098597464653e-10</v>
+        <v>2.188098597464615e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.188098597464653e-10</v>
+        <v>2.188098597464615e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>2.092607298610522e-10</v>
+        <v>2.092607298610537e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.189886891215258e-10</v>
+        <v>2.189886891215276e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>2.188137062112722e-10</v>
+        <v>2.188137062112705e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>1.97185307044743e-10</v>
+        <v>1.971853070447346e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.382762213004046e-10</v>
+        <v>2.382762213003984e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.988742807298814e-10</v>
+        <v>1.988742807298816e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.188098597464653e-10</v>
+        <v>2.188098597464615e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.385859520061583e-10</v>
+        <v>2.385859520061577e-10</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.265348067987618e-11</v>
+        <v>6.265348067987183e-11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.537628204950419e-11</v>
+        <v>5.537628204950129e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>6.87746233077885e-11</v>
+        <v>6.877462330778328e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>4.414583835109951e-11</v>
+        <v>4.414583835109932e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>6.17247123861368e-11</v>
+        <v>6.172471238613669e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>5.379768116441149e-11</v>
+        <v>5.379768116440508e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>6.114885823250159e-11</v>
+        <v>6.114885823249598e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>6.474243109952654e-11</v>
+        <v>6.474243109952446e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>5.488260941166624e-11</v>
+        <v>5.488260941166427e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>6.23073518115857e-11</v>
+        <v>6.230735181158046e-11</v>
       </c>
       <c r="L6" t="n">
-        <v>6.424806477613091e-11</v>
+        <v>6.424806477612646e-11</v>
       </c>
       <c r="M6" t="n">
-        <v>5.953220722495488e-11</v>
+        <v>5.953220722495447e-11</v>
       </c>
       <c r="N6" t="n">
-        <v>5.833354961189422e-11</v>
+        <v>5.833354961189194e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>5.093827496102439e-11</v>
+        <v>5.093827496102136e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>4.843953905535586e-11</v>
+        <v>4.843953905535236e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.66180414151246e-11</v>
+        <v>5.661804141512932e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>6.462613970282118e-11</v>
+        <v>6.462613970281663e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>6.174994727986293e-11</v>
+        <v>6.174994727986041e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>5.676798030939928e-11</v>
+        <v>5.676798030939724e-11</v>
       </c>
       <c r="U6" t="n">
-        <v>5.318056304868771e-11</v>
+        <v>5.318056304868467e-11</v>
       </c>
       <c r="V6" t="n">
-        <v>5.041341719822511e-11</v>
+        <v>5.041341719822716e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>7.754669534648176e-11</v>
+        <v>7.754669534647814e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>7.56760176818857e-11</v>
+        <v>7.56760176818806e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.832825728081736e-11</v>
+        <v>6.832825728081316e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.17291229262217e-11</v>
+        <v>6.172912292621665e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.132442819888167e-11</v>
+        <v>6.132442819887672e-11</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.314258775042867e-11</v>
+        <v>6.314258775042844e-11</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.400987373787847e-11</v>
+        <v>6.400987373786481e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>8.485466132923628e-11</v>
+        <v>8.485466132922943e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>8.358189245826438e-11</v>
+        <v>8.35818924582616e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>6.8793150531081e-11</v>
+        <v>6.879315053108053e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>6.572380886475168e-11</v>
+        <v>6.57238088647514e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>8.413874864013161e-11</v>
+        <v>8.413874864012764e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>8.358189245826438e-11</v>
+        <v>8.35818924582616e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>8.358189245826438e-11</v>
+        <v>8.35818924582616e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>7.81933036536012e-11</v>
+        <v>7.819330365359671e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>8.358189245826438e-11</v>
+        <v>8.35818924582616e-11</v>
       </c>
       <c r="L7" t="n">
-        <v>8.358189245826438e-11</v>
+        <v>8.35818924582616e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>8.119863886929424e-11</v>
+        <v>8.119863886929382e-11</v>
       </c>
       <c r="N7" t="n">
-        <v>6.841030362317201e-11</v>
+        <v>6.84103036231687e-11</v>
       </c>
       <c r="O7" t="n">
-        <v>6.907805856915712e-11</v>
+        <v>6.907805856915664e-11</v>
       </c>
       <c r="P7" t="n">
-        <v>6.805606623183213e-11</v>
+        <v>6.805606623183224e-11</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.016352534920395e-11</v>
+        <v>6.016352534920466e-11</v>
       </c>
       <c r="R7" t="n">
-        <v>8.358189245826438e-11</v>
+        <v>8.35818924582616e-11</v>
       </c>
       <c r="S7" t="n">
-        <v>8.358189245826438e-11</v>
+        <v>8.35818924582616e-11</v>
       </c>
       <c r="T7" t="n">
-        <v>8.358189245826438e-11</v>
+        <v>8.35818924582616e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>7.053123317303455e-11</v>
+        <v>7.053123317303488e-11</v>
       </c>
       <c r="V7" t="n">
-        <v>7.016310547366774e-11</v>
+        <v>7.016310547366565e-11</v>
       </c>
       <c r="W7" t="n">
-        <v>8.008420952325436e-11</v>
+        <v>8.008420952325103e-11</v>
       </c>
       <c r="X7" t="n">
-        <v>5.845581035672076e-11</v>
+        <v>5.84558103567155e-11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.030482540122013e-10</v>
+        <v>1.030482540121984e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.364631344168296e-11</v>
+        <v>6.364631344168021e-11</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.358189245826438e-11</v>
+        <v>8.35818924582616e-11</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.033579847179575e-10</v>
+        <v>1.033579847179572e-10</v>
       </c>
     </row>
   </sheetData>
@@ -5377,82 +5377,82 @@
         <v>1.259337253885548e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>9.364008956114663e-11</v>
+        <v>9.364008956114654e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.299513032129563e-10</v>
+        <v>1.299513032129514e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>8.268308802499585e-11</v>
+        <v>8.268308802499581e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.032112410240012e-10</v>
+        <v>1.032112410240011e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>1.162807981742492e-10</v>
+        <v>1.162807981742446e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>1.026873108160213e-10</v>
+        <v>1.026873108160271e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>1.155760705401053e-10</v>
+        <v>1.155760705401028e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>1.112402492926359e-10</v>
+        <v>1.112402492926428e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.050577661338799e-10</v>
+        <v>1.050577661338766e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>1.086555133127464e-10</v>
+        <v>1.086555133127446e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>9.952847570558054e-11</v>
+        <v>9.952847570558081e-11</v>
       </c>
       <c r="N2" t="n">
-        <v>9.766007419419218e-11</v>
+        <v>9.766007419418957e-11</v>
       </c>
       <c r="O2" t="n">
-        <v>8.843333092714987e-11</v>
+        <v>8.843333092714466e-11</v>
       </c>
       <c r="P2" t="n">
-        <v>8.533822069397758e-11</v>
+        <v>8.533822069397826e-11</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.248198062693398e-11</v>
+        <v>9.24819806269307e-11</v>
       </c>
       <c r="R2" t="n">
-        <v>1.260048932738633e-10</v>
+        <v>1.260048932738631e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>1.047570334801359e-10</v>
+        <v>1.047570334801293e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>9.588899388651822e-11</v>
+        <v>9.588899388651363e-11</v>
       </c>
       <c r="U2" t="n">
-        <v>9.990925436618178e-11</v>
+        <v>9.990925436617704e-11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.010293831273202e-10</v>
+        <v>1.010293831273203e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>2.701431961829585e-10</v>
+        <v>2.701431961829567e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>1.690490777357605e-10</v>
+        <v>1.690490777357565e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.371537732284781e-10</v>
+        <v>1.371537732284753e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.047148652895214e-10</v>
+        <v>1.047148652895138e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.09438506172365e-10</v>
+        <v>1.094385061723633e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.269837405096517e-10</v>
+        <v>1.269837405096515e-10</v>
       </c>
     </row>
     <row r="3">
@@ -5462,85 +5462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.136682690957336e-10</v>
+        <v>1.136682690957349e-10</v>
       </c>
       <c r="C3" t="n">
         <v>1.6826108646465e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>1.670065549073322e-10</v>
+        <v>1.670065549073252e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.343397237434108e-10</v>
+        <v>1.343397237434107e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.206220638762557e-10</v>
+        <v>1.206220638762556e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>1.780665959374087e-10</v>
+        <v>1.780665959374042e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.670065549073322e-10</v>
+        <v>1.670065549073252e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.670065549073322e-10</v>
+        <v>1.670065549073252e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.650391181409568e-10</v>
+        <v>1.650391181409598e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.670065549073322e-10</v>
+        <v>1.670065549073252e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.670065549073322e-10</v>
+        <v>1.670065549073252e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>1.646335567583092e-10</v>
+        <v>1.646335567583094e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>1.256604601040866e-10</v>
+        <v>1.256604601040806e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.370227259613073e-10</v>
+        <v>1.37022725961289e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.342375600485156e-10</v>
+        <v>1.342375600485125e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.03186078545287e-10</v>
+        <v>1.031860785452809e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.670065549073322e-10</v>
+        <v>1.670065549073252e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.670065549073322e-10</v>
+        <v>1.670065549073252e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>1.670065549073322e-10</v>
+        <v>1.670065549073252e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.409840484062748e-10</v>
+        <v>1.409840484062717e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>1.478013307600846e-10</v>
+        <v>1.478013307600845e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.670170374148173e-10</v>
+        <v>1.670170374148007e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>1.080746384283518e-10</v>
+        <v>1.080746384283529e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.200587564963078e-10</v>
+        <v>2.200587564962996e-10</v>
       </c>
       <c r="Z3" t="n">
         <v>1.126774830524162e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.670065549073322e-10</v>
+        <v>1.670065549073252e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.220779053947974e-10</v>
+        <v>2.220779053947982e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.04179066780008e-10</v>
+        <v>2.041790667800078e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.932056852680664e-10</v>
+        <v>1.932056852680673e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.056434267202229e-10</v>
+        <v>2.056434267202192e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.857037720941029e-10</v>
+        <v>1.857037720941049e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.950354331871564e-10</v>
+        <v>1.950354331871576e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>2.006606881607906e-10</v>
+        <v>2.006606881607868e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.957060216415041e-10</v>
+        <v>1.957060216415032e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>2.004038232134725e-10</v>
+        <v>2.004038232134705e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>1.990431996687009e-10</v>
+        <v>1.990431996686967e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.96570024769573e-10</v>
+        <v>1.965700247695648e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>1.978813613693874e-10</v>
+        <v>1.978813613693847e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>1.930465951478062e-10</v>
+        <v>1.930465951478073e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.938736529256395e-10</v>
+        <v>1.938736529256363e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>1.905106133506905e-10</v>
+        <v>1.905106133506878e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>1.893824820153234e-10</v>
+        <v>1.893824820153179e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.919862986246172e-10</v>
+        <v>1.919862986246151e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.042050066385092e-10</v>
+        <v>2.042050066385071e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>1.964604112486593e-10</v>
+        <v>1.964604112486559e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>1.93228114950565e-10</v>
+        <v>1.932281149505631e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>1.946934526871199e-10</v>
+        <v>1.946934526871158e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>2.019612189863473e-10</v>
+        <v>2.019612189863489e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>2.567417254914671e-10</v>
+        <v>2.567417254914654e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>2.198941064245406e-10</v>
+        <v>2.198941064245338e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.082686424652075e-10</v>
+        <v>2.082686424652042e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.964450414383496e-10</v>
+        <v>1.964450414383422e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.98166753072356e-10</v>
+        <v>1.981667530723461e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.041519122206323e-10</v>
+        <v>2.041519122206319e-10</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.997084519895388e-10</v>
+        <v>1.997084519895353e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>2.204041623954086e-10</v>
+        <v>2.204041623954088e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.191496308380869e-10</v>
+        <v>2.191496308380854e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.045320092306248e-10</v>
+        <v>2.045320092306254e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.013814736686003e-10</v>
+        <v>2.013814736686002e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.231808859199896e-10</v>
+        <v>2.231808859199916e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>2.191496308380869e-10</v>
+        <v>2.191496308380854e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.191496308380869e-10</v>
+        <v>2.191496308380854e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>2.186522556256997e-10</v>
+        <v>2.186522556256955e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>2.191496308380869e-10</v>
+        <v>2.191496308380854e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>2.191496308380869e-10</v>
+        <v>2.191496308380854e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.167766326890651e-10</v>
+        <v>2.16776632689067e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>2.040794647926518e-10</v>
+        <v>2.040794647926576e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.08220877275144e-10</v>
+        <v>2.082208772751502e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>2.072057170050254e-10</v>
+        <v>2.072057170050132e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.958878166219934e-10</v>
+        <v>1.958878166219906e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>2.191496308380869e-10</v>
+        <v>2.191496308380854e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>2.191496308380869e-10</v>
+        <v>2.191496308380854e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.191496308380869e-10</v>
+        <v>2.191496308380854e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>2.096647327901501e-10</v>
+        <v>2.096647327901483e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.190090446745521e-10</v>
+        <v>2.190090446745542e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>2.191534515889697e-10</v>
+        <v>2.191534515889676e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>1.976696392950082e-10</v>
+        <v>1.976696392949985e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.384865353468697e-10</v>
+        <v>2.384865353468621e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.993473221111427e-10</v>
+        <v>1.993473221111413e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.191496308380869e-10</v>
+        <v>2.191496308380854e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.388126186692066e-10</v>
+        <v>2.388126186692062e-10</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.828998693746149e-11</v>
+        <v>6.828998693744633e-11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.731660542550621e-11</v>
+        <v>5.731660542550624e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>6.975434687767154e-11</v>
+        <v>6.975434687765789e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>4.981469225154371e-11</v>
+        <v>4.981469225154379e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>5.914635334459612e-11</v>
+        <v>5.91463533445963e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>6.127186830729228e-11</v>
+        <v>6.12718683072918e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>5.981694179895237e-11</v>
+        <v>5.981694179894163e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>6.451474337092629e-11</v>
+        <v>6.451474337090948e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>5.830145000190284e-11</v>
+        <v>5.830145000189956e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>6.068094492702116e-11</v>
+        <v>6.068094492700384e-11</v>
       </c>
       <c r="L6" t="n">
-        <v>6.199228152683967e-11</v>
+        <v>6.199228152682309e-11</v>
       </c>
       <c r="M6" t="n">
-        <v>5.715751530524564e-11</v>
+        <v>5.715751530524608e-11</v>
       </c>
       <c r="N6" t="n">
-        <v>5.798457308308993e-11</v>
+        <v>5.798457308307487e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>5.11217934971958e-11</v>
+        <v>5.112179349719294e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>4.999366216183042e-11</v>
+        <v>4.999366216182328e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.609721878206553e-11</v>
+        <v>5.609721878205352e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>6.831592679595973e-11</v>
+        <v>6.831592679594567e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>6.057133140610931e-11</v>
+        <v>6.057133140609437e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>5.733903510801346e-11</v>
+        <v>5.733903510800193e-11</v>
       </c>
       <c r="U6" t="n">
-        <v>5.530463283362495e-11</v>
+        <v>5.530463283362117e-11</v>
       </c>
       <c r="V6" t="n">
-        <v>5.292273509510436e-11</v>
+        <v>5.292273509510424e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.173529056379742e-10</v>
+        <v>1.173529056379706e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>8.050528657105052e-11</v>
+        <v>8.050528657103927e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.237956262265967e-11</v>
+        <v>7.23795626226431e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.055596159578918e-11</v>
+        <v>6.055596159578093e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.227767322980221e-11</v>
+        <v>6.22776732297847e-11</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.826283237807098e-11</v>
+        <v>6.826283237807077e-11</v>
       </c>
     </row>
     <row r="7">
@@ -5814,82 +5814,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.381937214697537e-11</v>
+        <v>6.381937214697388e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>8.451508255284805e-11</v>
+        <v>8.451508255284796e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>8.326055099552694e-11</v>
+        <v>8.326055099552373e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>6.864292938806436e-11</v>
+        <v>6.864292938806435e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>6.549239382603865e-11</v>
+        <v>6.549239382603881e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>8.379206606649647e-11</v>
+        <v>8.379206606649681e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>8.326055099552694e-11</v>
+        <v>8.326055099552373e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>8.326055099552694e-11</v>
+        <v>8.326055099552373e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>7.791050595889971e-11</v>
+        <v>7.791050595889855e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>8.326055099552694e-11</v>
+        <v>8.326055099552373e-11</v>
       </c>
       <c r="L7" t="n">
-        <v>8.326055099552694e-11</v>
+        <v>8.326055099552373e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>8.08875528465051e-11</v>
+        <v>8.08875528465059e-11</v>
       </c>
       <c r="N7" t="n">
-        <v>6.819038495010791e-11</v>
+        <v>6.819038495009677e-11</v>
       </c>
       <c r="O7" t="n">
-        <v>6.883205742165321e-11</v>
+        <v>6.883205742165546e-11</v>
       </c>
       <c r="P7" t="n">
-        <v>6.781689715152861e-11</v>
+        <v>6.781689715151808e-11</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.999873677942973e-11</v>
+        <v>5.99987367794295e-11</v>
       </c>
       <c r="R7" t="n">
-        <v>8.326055099552694e-11</v>
+        <v>8.326055099552373e-11</v>
       </c>
       <c r="S7" t="n">
-        <v>8.326055099552694e-11</v>
+        <v>8.326055099552373e-11</v>
       </c>
       <c r="T7" t="n">
-        <v>8.326055099552694e-11</v>
+        <v>8.326055099552373e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>7.027591293665697e-11</v>
+        <v>7.027591293665393e-11</v>
       </c>
       <c r="V7" t="n">
-        <v>6.997056078330877e-11</v>
+        <v>6.997056078330853e-11</v>
       </c>
       <c r="W7" t="n">
-        <v>7.976463173547263e-11</v>
+        <v>7.976463173547224e-11</v>
       </c>
       <c r="X7" t="n">
-        <v>5.828081944151297e-11</v>
+        <v>5.828081944150353e-11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.025974555043163e-10</v>
+        <v>1.025974555043006e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.345824226857625e-11</v>
+        <v>6.345824226858005e-11</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.326055099552694e-11</v>
+        <v>8.326055099552373e-11</v>
       </c>
       <c r="AB7" t="n">
         <v>1.029235388266451e-10</v>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.425648941999856e-10</v>
+        <v>1.425648941999909e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>8.278911752834741e-11</v>
+        <v>8.278911752836674e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.390134155509951e-10</v>
+        <v>1.390134155510076e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>8.630691161993037e-11</v>
+        <v>8.630691161994663e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.029980564482558e-10</v>
+        <v>1.029980564482559e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>2.10018799622866e-10</v>
+        <v>2.100187996228784e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>9.739000799396526e-11</v>
+        <v>9.739000799397655e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>1.380546832902089e-10</v>
+        <v>1.380546832902193e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>1.723302040209535e-10</v>
+        <v>1.723302040209625e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.914393873271418e-10</v>
+        <v>1.914393873271524e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>2.47335034312156e-10</v>
+        <v>2.473350343121615e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>3.016567170511024e-10</v>
+        <v>3.016567170511028e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>1.554242209336996e-10</v>
+        <v>1.554242209337096e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>1.108695258085219e-10</v>
+        <v>1.108695258085314e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>1.551660087618545e-10</v>
+        <v>1.551660087618612e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.101174481168819e-10</v>
+        <v>1.101174481168945e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>1.069676263188929e-10</v>
+        <v>1.069676263188877e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>1.430734980742058e-10</v>
+        <v>1.430734980742168e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>1.175374065079225e-10</v>
+        <v>1.175374065079374e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>2.347749993752809e-10</v>
+        <v>2.347749993752933e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>9.937029360425996e-11</v>
+        <v>9.937029360426197e-11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.573130834297082e-10</v>
+        <v>1.573130834297291e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>1.804659780505553e-10</v>
+        <v>1.804659780505892e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.522912893564292e-10</v>
+        <v>1.522912893564392e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.370688352093713e-10</v>
+        <v>1.370688352093708e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.017347872469512e-10</v>
+        <v>1.017347872469619e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.768696392508247e-10</v>
+        <v>3.768696392508248e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.223739680860825e-10</v>
+        <v>1.223739680861004e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>1.81022658408339e-10</v>
+        <v>1.810226584083429e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>1.798354116796705e-10</v>
+        <v>1.798354116796804e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.44527165607864e-10</v>
+        <v>1.445271656078702e-10</v>
       </c>
       <c r="F3" t="n">
         <v>1.29756525605118e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>1.917504163358573e-10</v>
+        <v>1.917504163358594e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.798354116796705e-10</v>
+        <v>1.798354116796804e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.798354116796705e-10</v>
+        <v>1.798354116796804e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.776837433508226e-10</v>
+        <v>1.776837433508247e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.798354116796705e-10</v>
+        <v>1.798354116796804e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.798354116796705e-10</v>
+        <v>1.798354116796804e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>1.777501027533292e-10</v>
+        <v>1.777501027533295e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>1.352931798065494e-10</v>
+        <v>1.352931798065584e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.475337718830599e-10</v>
+        <v>1.475337718830652e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.445333069905004e-10</v>
+        <v>1.445333069905129e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.110814829245066e-10</v>
+        <v>1.110814829245078e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.798354116796705e-10</v>
+        <v>1.798354116796804e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.798354116796705e-10</v>
+        <v>1.798354116796804e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>1.798354116796705e-10</v>
+        <v>1.798354116796804e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.51789863422481e-10</v>
+        <v>1.517898634224804e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>1.589953010520501e-10</v>
+        <v>1.589953010520575e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.79846704507522e-10</v>
+        <v>1.798467045075395e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>1.163479384122087e-10</v>
+        <v>1.16347938412222e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.36969069956218e-10</v>
+        <v>2.369690699562228e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.213065922699709e-10</v>
+        <v>1.213065922699723e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.798354116796705e-10</v>
+        <v>1.798354116796804e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.399652343835817e-10</v>
+        <v>2.399652343835823e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.193956107210163e-10</v>
+        <v>2.19395610721031e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.983625512842361e-10</v>
+        <v>1.983625512842548e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181011384570236e-10</v>
+        <v>2.181011384570455e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.958958817954829e-10</v>
+        <v>1.958958817955004e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.039766773880465e-10</v>
+        <v>2.03976677388051e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>2.43981767163909e-10</v>
+        <v>2.43981767163923e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>2.029298951692162e-10</v>
+        <v>2.029298951692352e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>2.177516918059722e-10</v>
+        <v>2.177516918059942e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>2.299118566379294e-10</v>
+        <v>2.299118566379333e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>2.37209789552588e-10</v>
+        <v>2.372097895526066e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>2.575830965187908e-10</v>
+        <v>2.575830965188177e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>2.76057473690122e-10</v>
+        <v>2.760574736901336e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>2.240826843136173e-10</v>
+        <v>2.240826843136331e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>2.078430211281322e-10</v>
+        <v>2.078430211281499e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2398856900906e-10</v>
+        <v>2.239885690090773e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.075688976408768e-10</v>
+        <v>2.075688976408907e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.064208245825804e-10</v>
+        <v>2.064208245825991e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>2.195809908608382e-10</v>
+        <v>2.195809908608569e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>2.102733853448575e-10</v>
+        <v>2.10273385344876e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>2.530051112716861e-10</v>
+        <v>2.530051112717068e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>2.07290160230675e-10</v>
+        <v>2.072901602306748e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>2.247711525132688e-10</v>
+        <v>2.247711525132958e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>2.33210110727555e-10</v>
+        <v>2.332101107275807e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.229407675424395e-10</v>
+        <v>2.229407675424628e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.173923617569115e-10</v>
+        <v>2.173923617569373e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.045135161879574e-10</v>
+        <v>2.045135161879763e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.048646463777552e-10</v>
+        <v>3.048646463777602e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.120362552463202e-10</v>
+        <v>2.12036255246347e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>2.341675234185188e-10</v>
+        <v>2.341675234185294e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.329802766898496e-10</v>
+        <v>2.329802766898638e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.171164807173487e-10</v>
+        <v>2.171164807173648e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.137298251819108e-10</v>
+        <v>2.137298251819163e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.373231559739798e-10</v>
+        <v>2.373231559739966e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>2.329802766898496e-10</v>
+        <v>2.329802766898638e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.329802766898496e-10</v>
+        <v>2.329802766898638e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>2.318631588592313e-10</v>
+        <v>2.318631588592498e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>2.329802766898496e-10</v>
+        <v>2.329802766898638e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>2.329802766898496e-10</v>
+        <v>2.329802766898638e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.308949677635084e-10</v>
+        <v>2.308949677635138e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>2.167451562133906e-10</v>
+        <v>2.167451562134031e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.212067082889904e-10</v>
+        <v>2.212067082889936e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>2.201130740688885e-10</v>
+        <v>2.201130740689e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.079202770079827e-10</v>
+        <v>2.07920277008e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>2.329802766898496e-10</v>
+        <v>2.329802766898638e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>2.329802766898496e-10</v>
+        <v>2.329802766898638e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.329802766898496e-10</v>
+        <v>2.329802766898638e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>2.227580036775589e-10</v>
+        <v>2.227580036775767e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.290227752932099e-10</v>
+        <v>2.290227752932166e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>2.329843927929916e-10</v>
+        <v>2.329843927930103e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>2.098398381914109e-10</v>
+        <v>2.098398381914338e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.538048242343634e-10</v>
+        <v>2.538048242343678e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.116472092951111e-10</v>
+        <v>2.11647209295134e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.329802766898496e-10</v>
+        <v>2.329802766898638e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.549645984163302e-10</v>
+        <v>2.549645984163389e-10</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.582510864938748e-11</v>
+        <v>7.582510864940517e-11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.479204921262108e-11</v>
+        <v>5.479204921262453e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>7.453063638540478e-11</v>
+        <v>7.453063638541911e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>5.232537972386711e-11</v>
+        <v>5.232537972387372e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>6.040617531642403e-11</v>
+        <v>6.040617531642396e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>9.684688509690877e-11</v>
+        <v>9.684688509692091e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>5.93593930975967e-11</v>
+        <v>5.935939309760842e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>7.41811897343519e-11</v>
+        <v>7.418118973436386e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>8.18622094686501e-11</v>
+        <v>8.186220946866114e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>9.363928748096933e-11</v>
+        <v>9.363928748098001e-11</v>
       </c>
       <c r="L6" t="n">
-        <v>1.140125944471942e-10</v>
+        <v>1.140125944471918e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.324869716185024e-10</v>
+        <v>1.324869716185021e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>8.051218224199556e-11</v>
+        <v>8.051218224200726e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>6.070813906113465e-11</v>
+        <v>6.070813906114657e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>7.685368694206024e-11</v>
+        <v>7.685368694206901e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.399839556925115e-11</v>
+        <v>6.399839556926506e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>6.285032251096023e-11</v>
+        <v>6.285032251097428e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>7.60104887892206e-11</v>
+        <v>7.601048878923156e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>6.670288327323773e-11</v>
+        <v>6.670288327324986e-11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.058702292046884e-10</v>
+        <v>1.058702292046979e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.341538461945233e-11</v>
+        <v>5.341538461944937e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>7.763627044627086e-11</v>
+        <v>7.763627044628977e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>8.607522866055388e-11</v>
+        <v>8.60752286605736e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.937026547082006e-11</v>
+        <v>7.937026547083181e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.382185968529155e-11</v>
+        <v>7.382185968530689e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.094301411633355e-11</v>
+        <v>6.094301411634874e-11</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.612941443061335e-10</v>
+        <v>1.612941443061338e-10</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.846575317470092e-11</v>
+        <v>6.846575317471745e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>9.059702134689583e-11</v>
+        <v>9.05970213469002e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>8.940977461822816e-11</v>
+        <v>8.940977461823892e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>7.354597864572775e-11</v>
+        <v>7.354597864573315e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>7.015932311029131e-11</v>
+        <v>7.015932311029143e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>9.018827390698015e-11</v>
+        <v>9.018827390699207e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>8.940977461822816e-11</v>
+        <v>8.940977461823892e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>8.940977461822816e-11</v>
+        <v>8.940977461823892e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>8.381351168995511e-11</v>
+        <v>8.381351168996219e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>8.940977461822816e-11</v>
+        <v>8.940977461823892e-11</v>
       </c>
       <c r="L7" t="n">
-        <v>8.940977461822816e-11</v>
+        <v>8.940977461823892e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>8.732446569188793e-11</v>
+        <v>8.732446569188801e-11</v>
       </c>
       <c r="N7" t="n">
-        <v>7.317465414176982e-11</v>
+        <v>7.317465414177711e-11</v>
       </c>
       <c r="O7" t="n">
-        <v>7.407182622198942e-11</v>
+        <v>7.407182622199072e-11</v>
       </c>
       <c r="P7" t="n">
-        <v>7.297819200188802e-11</v>
+        <v>7.297819200189274e-11</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.434977493636325e-11</v>
+        <v>6.434977493637276e-11</v>
       </c>
       <c r="R7" t="n">
-        <v>8.940977461822816e-11</v>
+        <v>8.940977461823892e-11</v>
       </c>
       <c r="S7" t="n">
-        <v>8.940977461822816e-11</v>
+        <v>8.940977461823892e-11</v>
       </c>
       <c r="T7" t="n">
-        <v>8.940977461822816e-11</v>
+        <v>8.940977461823892e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>7.56231216105582e-11</v>
+        <v>7.562312161057002e-11</v>
       </c>
       <c r="V7" t="n">
-        <v>7.514799968198819e-11</v>
+        <v>7.514799968198558e-11</v>
       </c>
       <c r="W7" t="n">
-        <v>8.584951072599452e-11</v>
+        <v>8.584951072600687e-11</v>
       </c>
       <c r="X7" t="n">
-        <v>6.270495612440953e-11</v>
+        <v>6.270495612442624e-11</v>
       </c>
       <c r="Y7" t="n">
         <v>1.102343221627414e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.807670722348827e-11</v>
+        <v>6.807670722350361e-11</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.940977461822816e-11</v>
+        <v>8.940977461823892e-11</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.113940963447103e-10</v>
+        <v>1.113940963447107e-10</v>
       </c>
     </row>
   </sheetData>
@@ -6742,82 +6742,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.760273193223941e-11</v>
+        <v>9.760273193224101e-11</v>
       </c>
       <c r="C2" t="n">
-        <v>9.46623817850931e-11</v>
+        <v>9.466238178509325e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.191137670933598e-10</v>
+        <v>1.191137670933617e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>7.65122595681444e-11</v>
+        <v>7.651225956814453e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.035505493673781e-10</v>
+        <v>1.035505493673782e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>1.78568166432532e-10</v>
+        <v>1.78568166432534e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>9.194014818166964e-11</v>
+        <v>9.194014818167142e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>1.152799100704827e-10</v>
+        <v>1.152799100704847e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>1.315238601749738e-10</v>
+        <v>1.315238601749734e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.312558737787931e-10</v>
+        <v>1.31255873778795e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>1.563815428302767e-10</v>
+        <v>1.563815428302785e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>1.316050002103043e-10</v>
+        <v>1.316050002103045e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>9.136295745091873e-11</v>
+        <v>9.136295745092004e-11</v>
       </c>
       <c r="O2" t="n">
-        <v>8.24222144035873e-11</v>
+        <v>8.242221440358921e-11</v>
       </c>
       <c r="P2" t="n">
-        <v>1.215817935818632e-10</v>
+        <v>1.215817935818649e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.166106086072129e-10</v>
+        <v>1.16610608607215e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>1.139523759803948e-10</v>
+        <v>1.139523759803967e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>1.124740472208988e-10</v>
+        <v>1.124740472209007e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>9.653310648774235e-11</v>
+        <v>9.653310648774257e-11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.144367657634807e-10</v>
+        <v>1.144367657634832e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>9.40524473167307e-11</v>
+        <v>9.405244731673063e-11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.566205129057799e-10</v>
+        <v>1.566205129057814e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>1.645073945381791e-10</v>
+        <v>1.645073945381809e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.043539115970891e-10</v>
+        <v>2.043539115970908e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.052256358086831e-10</v>
+        <v>1.05225635808685e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.025385963625345e-10</v>
+        <v>1.025385963625362e-10</v>
       </c>
       <c r="AB2" t="n">
         <v>2.795921801736628e-10</v>
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.198473589744829e-10</v>
+        <v>1.198473589744844e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>1.77306750433876e-10</v>
+        <v>1.773067504338762e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>1.760176728543077e-10</v>
+        <v>1.760176728543099e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.415933710822825e-10</v>
+        <v>1.415933710822828e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.271633793817118e-10</v>
+        <v>1.271633793817121e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>1.876649533533632e-10</v>
+        <v>1.876649533533657e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.760176728543077e-10</v>
+        <v>1.760176728543099e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.760176728543077e-10</v>
+        <v>1.760176728543099e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.739399639168268e-10</v>
+        <v>1.739399639168276e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.760176728543077e-10</v>
+        <v>1.760176728543099e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>1.760176728543077e-10</v>
+        <v>1.760176728543099e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>1.736116288293831e-10</v>
+        <v>1.736116288293834e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>1.324762825104765e-10</v>
+        <v>1.324762825104781e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.444418346442227e-10</v>
+        <v>1.444418346442238e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.41508788687568e-10</v>
+        <v>1.415087886875713e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.088086102704497e-10</v>
+        <v>1.088086102704518e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.760176728543077e-10</v>
+        <v>1.760176728543099e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.760176728543077e-10</v>
+        <v>1.760176728543099e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>1.760176728543077e-10</v>
+        <v>1.760176728543099e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.486069713775401e-10</v>
+        <v>1.486069713775417e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>1.557560557033315e-10</v>
+        <v>1.557560557033317e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.760287119374998e-10</v>
+        <v>1.760287119375025e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>1.139567311539487e-10</v>
+        <v>1.1395673115395e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.318755683071197e-10</v>
+        <v>2.318755683071219e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.188039665557351e-10</v>
+        <v>1.18803966555737e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.760176728543077e-10</v>
+        <v>1.760176728543099e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.345615512399285e-10</v>
+        <v>2.345615512399293e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6918,85 +6918,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.995351265657181e-10</v>
+        <v>1.995351265657209e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>1.992826274033475e-10</v>
+        <v>1.992826274033476e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.07375646286619e-10</v>
+        <v>2.073756462866216e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.889783921322187e-10</v>
+        <v>1.88978392132219e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.007912941598529e-10</v>
+        <v>2.007912941598532e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>2.290460766969421e-10</v>
+        <v>2.290460766969437e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.974711812820512e-10</v>
+        <v>1.974711812820526e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>2.059782504212023e-10</v>
+        <v>2.05978250421205e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>2.118034898911194e-10</v>
+        <v>2.118034898911237e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>2.11801301593644e-10</v>
+        <v>2.118013015936466e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>2.20959312922408e-10</v>
+        <v>2.209593129224106e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>2.103994848472483e-10</v>
+        <v>2.103994848472485e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.972608020384086e-10</v>
+        <v>1.972608020384107e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>1.940020061851614e-10</v>
+        <v>1.94002006185164e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>2.082752129606481e-10</v>
+        <v>2.082752129606508e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.064632744119892e-10</v>
+        <v>2.06463274411992e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.054943798340576e-10</v>
+        <v>2.0549437983406e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>2.049555463606339e-10</v>
+        <v>2.049555463606365e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>1.991452606513741e-10</v>
+        <v>1.991452606513763e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>2.056709342220001e-10</v>
+        <v>2.056709342220034e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>2.032897605459599e-10</v>
+        <v>2.0328976054596e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>2.210464147088003e-10</v>
+        <v>2.210464147088025e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>2.2392109045137e-10</v>
+        <v>2.239210904513726e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.384446780179159e-10</v>
+        <v>2.38444678017918e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.023135855160254e-10</v>
+        <v>2.023135855160279e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.013341911907145e-10</v>
+        <v>2.013341911907171e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.657850748216378e-10</v>
+        <v>2.65785074821638e-10</v>
       </c>
     </row>
     <row r="5">
@@ -7006,85 +7006,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.076430319130186e-10</v>
+        <v>2.076430319130198e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>2.294055293166557e-10</v>
+        <v>2.294055293166558e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.281164517370887e-10</v>
+        <v>2.281164517370899e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.12699693058127e-10</v>
+        <v>2.126996930581274e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.093978934242285e-10</v>
+        <v>2.09397893424229e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.323617487097213e-10</v>
+        <v>2.323617487097226e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>2.281164517370887e-10</v>
+        <v>2.281164517370899e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>2.281164517370887e-10</v>
+        <v>2.281164517370899e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>2.27263661629988e-10</v>
+        <v>2.272636616299929e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>2.281164517370887e-10</v>
+        <v>2.281164517370899e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>2.281164517370887e-10</v>
+        <v>2.281164517370899e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.257104077121648e-10</v>
+        <v>2.257104077121652e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>2.122461262455819e-10</v>
+        <v>2.122461262455822e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.166074294917241e-10</v>
+        <v>2.166074294917254e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>2.155383686820882e-10</v>
+        <v>2.155383686820901e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.0361953763393e-10</v>
+        <v>2.036195376339318e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>2.281164517370887e-10</v>
+        <v>2.281164517370899e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>2.281164517370887e-10</v>
+        <v>2.281164517370899e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.281164517370887e-10</v>
+        <v>2.281164517370899e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>2.181255729215128e-10</v>
+        <v>2.181255729215147e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.257800012425252e-10</v>
+        <v>2.257800012425249e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>2.281204753532833e-10</v>
+        <v>2.281204753532855e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>2.054959672436767e-10</v>
+        <v>2.054959672436792e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.484759987131142e-10</v>
+        <v>2.484759987131153e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.072627276285156e-10</v>
+        <v>2.072627276285188e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.281164517370887e-10</v>
+        <v>2.281164517370899e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.493719393516331e-10</v>
+        <v>2.493719393516338e-10</v>
       </c>
     </row>
     <row r="6">
@@ -7094,82 +7094,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.910194214565815e-11</v>
+        <v>5.910194214566007e-11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.884944298328774e-11</v>
+        <v>5.884944298328769e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>6.694246186655907e-11</v>
+        <v>6.69424618665607e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>4.854520771215921e-11</v>
+        <v>4.854520771215919e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>6.035810973979319e-11</v>
+        <v>6.035810973979325e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>8.506918912992447e-11</v>
+        <v>8.506918912992594e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>5.703799686199141e-11</v>
+        <v>5.70379968619923e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>6.554506600114259e-11</v>
+        <v>6.55450660011442e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>6.672066587613608e-11</v>
+        <v>6.672066587613695e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>7.136811717358442e-11</v>
+        <v>7.136811717358597e-11</v>
       </c>
       <c r="L6" t="n">
-        <v>8.05261285023481e-11</v>
+        <v>8.05261285023498e-11</v>
       </c>
       <c r="M6" t="n">
-        <v>6.996630042718833e-11</v>
+        <v>6.99663004271883e-11</v>
       </c>
       <c r="N6" t="n">
-        <v>5.68276176183487e-11</v>
+        <v>5.6827617618351e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>5.00251186181436e-11</v>
+        <v>5.002511861814604e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>6.429832539363045e-11</v>
+        <v>6.429832539363275e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.603008999192964e-11</v>
+        <v>6.603008999193124e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>6.506119541399785e-11</v>
+        <v>6.506119541399944e-11</v>
       </c>
       <c r="S6" t="n">
-        <v>6.452236194057429e-11</v>
+        <v>6.452236194057597e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>5.871207623131436e-11</v>
+        <v>5.871207623131707e-11</v>
       </c>
       <c r="U6" t="n">
-        <v>6.169404665498268e-11</v>
+        <v>6.169404665498569e-11</v>
       </c>
       <c r="V6" t="n">
-        <v>5.130167725075225e-11</v>
+        <v>5.130167725075223e-11</v>
       </c>
       <c r="W6" t="n">
-        <v>7.706952714178268e-11</v>
+        <v>7.706952714178482e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>7.994420288435246e-11</v>
+        <v>7.994420288435476e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.801149359785643e-11</v>
+        <v>9.801149359785908e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.188040109596574e-11</v>
+        <v>6.188040109596733e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.090100677065478e-11</v>
+        <v>6.090100677065635e-11</v>
       </c>
       <c r="AB6" t="n">
         <v>1.25351890401578e-10</v>
@@ -7182,85 +7182,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.720984749295879e-11</v>
+        <v>6.720984749295906e-11</v>
       </c>
       <c r="C7" t="n">
-        <v>8.897234489659592e-11</v>
+        <v>8.897234489659616e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>8.768326731702898e-11</v>
+        <v>8.768326731702915e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>7.226650863806732e-11</v>
+        <v>7.226650863806735e-11</v>
       </c>
       <c r="F7" t="n">
-        <v>6.896470900416867e-11</v>
+        <v>6.896470900416877e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>8.838486114270348e-11</v>
+        <v>8.838486114270475e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>8.768326731702898e-11</v>
+        <v>8.768326731702915e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>8.768326731702898e-11</v>
+        <v>8.768326731702915e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>8.218083761500499e-11</v>
+        <v>8.21808376150059e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>8.768326731702898e-11</v>
+        <v>8.768326731702915e-11</v>
       </c>
       <c r="L7" t="n">
-        <v>8.768326731702898e-11</v>
+        <v>8.768326731702915e-11</v>
       </c>
       <c r="M7" t="n">
-        <v>8.527722329210519e-11</v>
+        <v>8.527722329210531e-11</v>
       </c>
       <c r="N7" t="n">
-        <v>7.181294182552226e-11</v>
+        <v>7.181294182552149e-11</v>
       </c>
       <c r="O7" t="n">
-        <v>7.263054192470636e-11</v>
+        <v>7.263054192470749e-11</v>
       </c>
       <c r="P7" t="n">
-        <v>7.15614811150707e-11</v>
+        <v>7.156148111507218e-11</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.31863532138703e-11</v>
+        <v>6.318635321387098e-11</v>
       </c>
       <c r="R7" t="n">
-        <v>8.768326731702898e-11</v>
+        <v>8.768326731702915e-11</v>
       </c>
       <c r="S7" t="n">
-        <v>8.768326731702898e-11</v>
+        <v>8.768326731702915e-11</v>
       </c>
       <c r="T7" t="n">
-        <v>8.768326731702898e-11</v>
+        <v>8.768326731702915e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>7.414868535449539e-11</v>
+        <v>7.414868535449691e-11</v>
       </c>
       <c r="V7" t="n">
-        <v>7.379191794731686e-11</v>
+        <v>7.379191794731716e-11</v>
       </c>
       <c r="W7" t="n">
-        <v>8.414358778626603e-11</v>
+        <v>8.414358778626799e-11</v>
       </c>
       <c r="X7" t="n">
-        <v>6.151907967665884e-11</v>
+        <v>6.151907967666135e-11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.080428142930543e-10</v>
+        <v>1.080428142930546e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.682954320845607e-11</v>
+        <v>6.682954320845814e-11</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.768326731702898e-11</v>
+        <v>8.768326731702915e-11</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.089387549315737e-10</v>
+        <v>1.089387549315738e-10</v>
       </c>
     </row>
   </sheetData>
